--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -1650,7 +1650,7 @@
         <v>52</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">'Cost Structure'!$B$39</f>
+        <f aca="false">SeasonProfit</f>
         <v>42775.1553877422</v>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
         <v>55</v>
       </c>
       <c r="B17" s="18" t="n">
-        <f aca="false">'Cost Structure'!$B$13</f>
+        <f aca="false">TotalLaborRequired</f>
         <v>5276.82284632822</v>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
         <v>56</v>
       </c>
       <c r="B18" s="18" t="n">
-        <f aca="false">'Cost Structure'!$B$17</f>
+        <f aca="false">TotalLaborCapacity</f>
         <v>6480</v>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
         <v>58</v>
       </c>
       <c r="B20" s="19" t="n">
-        <f aca="false">'Cost Structure'!$B$16</f>
+        <f aca="false">TempWorkersNeeded</f>
         <v>4</v>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
         <v>68</v>
       </c>
       <c r="B13" s="22" t="n">
-        <f aca="false">B10+B11+B12</f>
+        <f aca="false">TomatoLaborHours+CarrotLaborHours+MesclunLaborHours</f>
         <v>5276.82284632822</v>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
         <v>69</v>
       </c>
       <c r="B14" s="21" t="n">
-        <f aca="false">MIN(B13,FarmerHours)</f>
+        <f aca="false">MIN(TotalLaborRequired,FarmerHours)</f>
         <v>720</v>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
         <v>70</v>
       </c>
       <c r="B15" s="21" t="n">
-        <f aca="false">MAX(B13-FarmerHours,0)</f>
+        <f aca="false">MAX(TotalLaborRequired-FarmerHours,0)</f>
         <v>4556.82284632822</v>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
         <v>58</v>
       </c>
       <c r="B16" s="10" t="n">
-        <f aca="false">IF(B15=0,0,MIN(MaxTempWorkers,ROUNDUP(B15/TempWorkerHours,0)))</f>
+        <f aca="false">IF(TempLaborHoursNeeded=0,0,MIN(MaxTempWorkers,ROUNDUP(TempLaborHoursNeeded/TempWorkerHours,0)))</f>
         <v>4</v>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
         <v>71</v>
       </c>
       <c r="B17" s="21" t="n">
-        <f aca="false">FarmerHours+B16*TempWorkerHours</f>
+        <f aca="false">FarmerHours+TempWorkersNeeded*TempWorkerHours</f>
         <v>6480</v>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
         <v>72</v>
       </c>
       <c r="B18" s="21" t="n">
-        <f aca="false">B17-B13</f>
+        <f aca="false">TotalLaborCapacity-TotalLaborRequired</f>
         <v>1203.17715367179</v>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
         <v>74</v>
       </c>
       <c r="B21" s="23" t="n">
-        <f aca="false">B14*FarmerRate</f>
+        <f aca="false">FarmerHoursUsed*FarmerRate</f>
         <v>24998.4</v>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
         <v>75</v>
       </c>
       <c r="B22" s="23" t="n">
-        <f aca="false">B15*TempRate</f>
+        <f aca="false">TempLaborHoursNeeded*TempRate</f>
         <v>79106.4446122578</v>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
         <v>76</v>
       </c>
       <c r="B23" s="24" t="n">
-        <f aca="false">B21+B22</f>
+        <f aca="false">FarmerLaborCost+TempLaborCost</f>
         <v>104104.844612258</v>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
         <v>77</v>
       </c>
       <c r="B24" s="25" t="n">
-        <f aca="false">IF(B13=0,0,B23/B13)</f>
+        <f aca="false">IF(TotalLaborRequired=0,0,TotalLaborCost/TotalLaborRequired)</f>
         <v>19.7286980525976</v>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
         <v>78</v>
       </c>
       <c r="B28" s="24" t="n">
-        <f aca="false">B25+B26+B27</f>
+        <f aca="false">TomatoFertilizerCost+CarrotFertilizerCost+MesclunFertilizerCost</f>
         <v>44000</v>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
         <v>79</v>
       </c>
       <c r="B30" s="24" t="n">
-        <f aca="false">B29+B28+B23</f>
+        <f aca="false">FixedCosts+TotalFertilizerCost+TotalLaborCost</f>
         <v>168104.844612258</v>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
         <v>84</v>
       </c>
       <c r="B36" s="24" t="n">
-        <f aca="false">B33+B34+B35</f>
+        <f aca="false">TomatoRevenue+CarrotRevenue+MesclunRevenue</f>
         <v>210880</v>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
         <v>86</v>
       </c>
       <c r="B39" s="27" t="n">
-        <f aca="false">B36-B30</f>
+        <f aca="false">TotalRevenue-TotalCost</f>
         <v>42775.1553877422</v>
       </c>
     </row>

--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -50,7 +50,9 @@
     <definedName function="false" hidden="false" name="TempLaborCost" vbProcedure="false">'Cost Structure'!$B$22</definedName>
     <definedName function="false" hidden="false" name="TempLaborHoursNeeded" vbProcedure="false">'Cost Structure'!$B$15</definedName>
     <definedName function="false" hidden="false" name="TempRate" vbProcedure="false">Inputs!$B$11</definedName>
+    <definedName function="false" hidden="false" name="TempWorkerEquivalent" vbProcedure="false">'Cost Structure'!$B$42</definedName>
     <definedName function="false" hidden="false" name="TempWorkerHours" vbProcedure="false">Inputs!$B$10</definedName>
+    <definedName function="false" hidden="false" name="TempWorkersForHiring" vbProcedure="false">'Cost Structure'!$B$43</definedName>
     <definedName function="false" hidden="false" name="TempWorkersNeeded" vbProcedure="false">'Cost Structure'!$B$16</definedName>
     <definedName function="false" hidden="false" name="TomatoBeds" vbProcedure="false">Optimization!$B$7</definedName>
     <definedName function="false" hidden="false" name="TomatoFertilizerCost" vbProcedure="false">'Cost Structure'!$B$25</definedName>
@@ -80,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="161">
   <si>
     <t xml:space="preserve">Marginal Analysis — Model Inputs</t>
   </si>
@@ -343,6 +345,15 @@
     <t xml:space="preserve">Season Profit</t>
   </si>
   <si>
+    <t xml:space="preserve">Temporary Labor — Fractional vs. Hiring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temp Worker-Equivalent Usage (fractional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temporary Workers Required for Hiring (whole)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Outputs — Summary Dashboard</t>
   </si>
   <si>
@@ -466,6 +477,57 @@
     <t xml:space="preserve">All Checks Pass?</t>
   </si>
   <si>
+    <t xml:space="preserve">Acceptance Tests (model-correctness checks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acceptance Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q=1 Tomato Labor = 99 hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hand check: TomatoBeds=1 should compute exactly 99 labor hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q=10 Tomato Labor ≈ 2,334.37 hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verifies the 10% diminishing-returns rate compounds with quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimal Allocation = 10 Tomato / 20 Carrot / 30 Mesclun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Published check figure for the optimized solution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Season Profit ≈ $42,762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Published check figure for optimized season profit (tolerance $5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomato P≈MC crossing at q=10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marginal Cost &lt;= Price at q=10, and Marginal Cost &gt; Price at q=11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrot P≈MC crossing at q=10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesclun P≈MC crossing at q=6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marginal Cost &lt;= Price at q=6, and Marginal Cost &gt; Price at q=7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All Acceptance Tests Pass?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Notes &amp; Audit Findings (build-time)</t>
   </si>
   <si>
@@ -484,7 +546,7 @@
     <t xml:space="preserve">3. Small profit discrepancy vs. the published check figure.</t>
   </si>
   <si>
-    <t xml:space="preserve">This workbook's formulas calculate Season Profit at 10/20/30 beds as $42,775.16. The spec's published check figure is "approximately $42,762" — a difference of about $13 (0.03%). The formulas were verified independently (hand recomputation and the Validation Rules checks below) and no error was found on this end; the small gap is most likely rounding in the spec author's own reference calculation. Flagging this for your manual audit rather than adjusting the model to force a match.</t>
+    <t xml:space="preserve">This workbook previously calculated Season Profit at 10/20/30 beds as $42,775.16 against the spec's published check figure of "approximately $42,762" — a difference of about $13. Per Professor Stauffer's Stage 1.2 review (PR #6), the gap was traced to three inputs carried at the case's rounded display precision (Farmer Labor Rate $34.72, Temporary Labor Rate $17.36, Carrot Base Labor 0.833) instead of their underlying derivations. The Inputs sheet now computes these as formulas ($50,000/1,440, $25,000/1,440, and 2.5/3), and Season Profit now resolves to approximately $42,761.66, reconciling with the published figure.</t>
   </si>
   <si>
     <t xml:space="preserve">4. Farm Profit Lab cross-check not performed.</t>
@@ -509,7 +571,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
@@ -517,7 +579,9 @@
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
     <numFmt numFmtId="170" formatCode="\$#,##0.0000"/>
-    <numFmt numFmtId="171" formatCode="General"/>
+    <numFmt numFmtId="171" formatCode="#,##0.00;\(#,##0.00\);\-"/>
+    <numFmt numFmtId="172" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="173" formatCode="General"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -691,7 +755,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -804,6 +868,22 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="170" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -812,7 +892,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -825,6 +905,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -845,7 +937,35 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF006100"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF9C0006"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -1210,7 +1330,8 @@
         <v>14</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>34.72</v>
+        <f aca="false">50000/1440</f>
+        <v>34.7222222222222</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>15</v>
@@ -1252,7 +1373,8 @@
         <v>20</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>17.36</v>
+        <f aca="false">25000/1440</f>
+        <v>17.3611111111111</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>15</v>
@@ -1380,7 +1502,8 @@
         <v>33</v>
       </c>
       <c r="B23" s="8" t="n">
-        <v>0.833</v>
+        <f aca="false">2.5/3</f>
+        <v>0.833333333333333</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>26</v>
@@ -1651,7 +1774,7 @@
       </c>
       <c r="B12" s="16" t="n">
         <f aca="false">SeasonProfit</f>
-        <v>42775.1553877422</v>
+        <v>42761.6646827451</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1673,7 +1796,7 @@
       </c>
       <c r="B17" s="18" t="n">
         <f aca="false">TotalLaborRequired</f>
-        <v>5276.82284632822</v>
+        <v>5277.21611427389</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1733,7 +1856,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
@@ -1815,7 +1938,7 @@
       </c>
       <c r="B11" s="21" t="n">
         <f aca="false">IF(CarrotBeds=0,0,CarrotBeds*Car_BaseLabor*SeasonLength*(1+Car_DR)^CarrotBeds)</f>
-        <v>982.776596228567</v>
+        <v>983.169864174237</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1833,7 +1956,7 @@
       </c>
       <c r="B13" s="22" t="n">
         <f aca="false">TomatoLaborHours+CarrotLaborHours+MesclunLaborHours</f>
-        <v>5276.82284632822</v>
+        <v>5277.21611427389</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1851,7 +1974,7 @@
       </c>
       <c r="B15" s="21" t="n">
         <f aca="false">MAX(TotalLaborRequired-FarmerHours,0)</f>
-        <v>4556.82284632822</v>
+        <v>4557.21611427389</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1878,7 +2001,7 @@
       </c>
       <c r="B18" s="21" t="n">
         <f aca="false">TotalLaborCapacity-TotalLaborRequired</f>
-        <v>1203.17715367179</v>
+        <v>1202.78388572612</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1893,7 +2016,7 @@
       </c>
       <c r="B21" s="23" t="n">
         <f aca="false">FarmerHoursUsed*FarmerRate</f>
-        <v>24998.4</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1902,7 +2025,7 @@
       </c>
       <c r="B22" s="23" t="n">
         <f aca="false">TempLaborHoursNeeded*TempRate</f>
-        <v>79106.4446122578</v>
+        <v>79118.335317255</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1911,7 +2034,7 @@
       </c>
       <c r="B23" s="24" t="n">
         <f aca="false">FarmerLaborCost+TempLaborCost</f>
-        <v>104104.844612258</v>
+        <v>104118.335317255</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1920,7 +2043,7 @@
       </c>
       <c r="B24" s="25" t="n">
         <f aca="false">IF(TotalLaborRequired=0,0,TotalLaborCost/TotalLaborRequired)</f>
-        <v>19.7286980525976</v>
+        <v>19.7297842390108</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1974,7 +2097,7 @@
       </c>
       <c r="B30" s="24" t="n">
         <f aca="false">FixedCosts+TotalFertilizerCost+TotalLaborCost</f>
-        <v>168104.844612258</v>
+        <v>168118.335317255</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2031,7 +2154,30 @@
       </c>
       <c r="B39" s="27" t="n">
         <f aca="false">TotalRevenue-TotalCost</f>
-        <v>42775.1553877422</v>
+        <v>42761.6646827451</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="28" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B42" s="30" t="n">
+        <f aca="false">TempLaborHoursNeeded/TempWorkerHours</f>
+        <v>3.1647334126902</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="B43" s="31" t="n">
+        <f aca="false">CEILING(TempWorkerEquivalent,1)</f>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2069,7 +2215,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2077,7 +2223,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7" t="s">
@@ -2114,7 +2260,7 @@
       </c>
       <c r="D5" s="18" t="n">
         <f aca="false">'Cost Structure'!B11</f>
-        <v>982.776596228567</v>
+        <v>983.169864174237</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2146,7 +2292,7 @@
       </c>
       <c r="D7" s="18" t="n">
         <f aca="false">TotalLaborRequired</f>
-        <v>5276.82284632822</v>
+        <v>5277.21611427389</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2168,7 +2314,7 @@
       </c>
       <c r="D9" s="18" t="n">
         <f aca="false">'Cost Structure'!B15</f>
-        <v>4556.82284632822</v>
+        <v>4557.21611427389</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2216,7 +2362,7 @@
       </c>
       <c r="D12" s="18" t="n">
         <f aca="false">'Cost Structure'!B18</f>
-        <v>1203.17715367179</v>
+        <v>1202.78388572612</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2253,7 +2399,7 @@
       </c>
       <c r="B16" s="26" t="n">
         <f aca="false">SeasonProfit</f>
-        <v>42775.1553877422</v>
+        <v>42761.6646827451</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>34</v>
@@ -2287,7 +2433,7 @@
       </c>
       <c r="D19" s="26" t="n">
         <f aca="false">'Cost Structure'!B21</f>
-        <v>24998.4</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2296,7 +2442,7 @@
       </c>
       <c r="D20" s="26" t="n">
         <f aca="false">'Cost Structure'!B22</f>
-        <v>79106.4446122578</v>
+        <v>79118.335317255</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2305,16 +2451,16 @@
       </c>
       <c r="D21" s="26" t="n">
         <f aca="false">'Cost Structure'!B23</f>
-        <v>104104.844612258</v>
+        <v>104118.335317255</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C22" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="28" t="n">
+      <c r="D22" s="32" t="n">
         <f aca="false">'Cost Structure'!B24</f>
-        <v>19.7286980525976</v>
+        <v>19.7297842390108</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2328,11 +2474,11 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C24" s="14" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D24" s="26" t="n">
         <f aca="false">'Cost Structure'!B30</f>
-        <v>168104.844612258</v>
+        <v>168118.335317255</v>
       </c>
     </row>
   </sheetData>
@@ -2380,7 +2526,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2399,7 +2545,7 @@
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -2418,64 +2564,64 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>69</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>74</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>76</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="29" t="n">
+      <c r="B6" s="33" t="n">
         <f aca="false">IF($A6=0,0,$A6*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A6)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="33" t="n">
         <f aca="false">MIN(B6,FarmerHours)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="33" t="n">
         <f aca="false">MAX(B6-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -2483,51 +2629,51 @@
         <f aca="false">IF(D6=0,0,ROUNDUP(D6/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F6" s="30" t="b">
+      <c r="F6" s="34" t="b">
         <f aca="false">AND(B6&lt;=MaxLaborCapacity,E6&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G6" s="31" t="n">
+      <c r="G6" s="35" t="n">
         <f aca="false">C6*FarmerRate</f>
         <v>0</v>
       </c>
-      <c r="H6" s="31" t="n">
+      <c r="H6" s="35" t="n">
         <f aca="false">D6*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I6" s="31" t="n">
+      <c r="I6" s="35" t="n">
         <f aca="false">$A6*Tom_Fert</f>
         <v>0</v>
       </c>
-      <c r="J6" s="31" t="n">
+      <c r="J6" s="35" t="n">
         <f aca="false">G6+H6</f>
         <v>0</v>
       </c>
-      <c r="K6" s="31" t="n">
+      <c r="K6" s="35" t="n">
         <f aca="false">FixedCosts+I6+J6</f>
         <v>20000</v>
       </c>
-      <c r="L6" s="32"/>
-      <c r="M6" s="31" t="n">
+      <c r="L6" s="36"/>
+      <c r="M6" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N6" s="32"/>
-      <c r="O6" s="32"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="33" t="n">
         <f aca="false">IF($A7=0,0,$A7*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A7)</f>
         <v>99</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="33" t="n">
         <f aca="false">MIN(B7,FarmerHours)</f>
         <v>99</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="33" t="n">
         <f aca="false">MAX(B7-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -2535,60 +2681,60 @@
         <f aca="false">IF(D7=0,0,ROUNDUP(D7/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F7" s="30" t="b">
+      <c r="F7" s="34" t="b">
         <f aca="false">AND(B7&lt;=MaxLaborCapacity,E7&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G7" s="31" t="n">
+      <c r="G7" s="35" t="n">
         <f aca="false">C7*FarmerRate</f>
-        <v>3437.28</v>
-      </c>
-      <c r="H7" s="31" t="n">
+        <v>3437.5</v>
+      </c>
+      <c r="H7" s="35" t="n">
         <f aca="false">D7*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I7" s="31" t="n">
+      <c r="I7" s="35" t="n">
         <f aca="false">$A7*Tom_Fert</f>
         <v>880</v>
       </c>
-      <c r="J7" s="31" t="n">
+      <c r="J7" s="35" t="n">
         <f aca="false">G7+H7</f>
-        <v>3437.28</v>
-      </c>
-      <c r="K7" s="31" t="n">
+        <v>3437.5</v>
+      </c>
+      <c r="K7" s="35" t="n">
         <f aca="false">FixedCosts+I7+J7</f>
-        <v>24317.28</v>
-      </c>
-      <c r="L7" s="31" t="n">
+        <v>24317.5</v>
+      </c>
+      <c r="L7" s="35" t="n">
         <f aca="false">K7-K6</f>
-        <v>4317.28</v>
-      </c>
-      <c r="M7" s="31" t="n">
+        <v>4317.5</v>
+      </c>
+      <c r="M7" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N7" s="30" t="b">
+      <c r="N7" s="34" t="b">
         <f aca="false">L7&lt;=M7</f>
         <v>1</v>
       </c>
-      <c r="O7" s="31" t="n">
+      <c r="O7" s="35" t="n">
         <f aca="false">ABS(M7-L7)</f>
-        <v>4482.72</v>
+        <v>4482.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="33" t="n">
         <f aca="false">IF($A8=0,0,$A8*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A8)</f>
         <v>217.8</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="33" t="n">
         <f aca="false">MIN(B8,FarmerHours)</f>
         <v>217.8</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="33" t="n">
         <f aca="false">MAX(B8-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -2596,60 +2742,60 @@
         <f aca="false">IF(D8=0,0,ROUNDUP(D8/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F8" s="30" t="b">
+      <c r="F8" s="34" t="b">
         <f aca="false">AND(B8&lt;=MaxLaborCapacity,E8&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G8" s="31" t="n">
+      <c r="G8" s="35" t="n">
         <f aca="false">C8*FarmerRate</f>
-        <v>7562.016</v>
-      </c>
-      <c r="H8" s="31" t="n">
+        <v>7562.5</v>
+      </c>
+      <c r="H8" s="35" t="n">
         <f aca="false">D8*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I8" s="31" t="n">
+      <c r="I8" s="35" t="n">
         <f aca="false">$A8*Tom_Fert</f>
         <v>1760</v>
       </c>
-      <c r="J8" s="31" t="n">
+      <c r="J8" s="35" t="n">
         <f aca="false">G8+H8</f>
-        <v>7562.016</v>
-      </c>
-      <c r="K8" s="31" t="n">
+        <v>7562.5</v>
+      </c>
+      <c r="K8" s="35" t="n">
         <f aca="false">FixedCosts+I8+J8</f>
-        <v>29322.016</v>
-      </c>
-      <c r="L8" s="31" t="n">
+        <v>29322.5</v>
+      </c>
+      <c r="L8" s="35" t="n">
         <f aca="false">K8-K7</f>
-        <v>5004.736</v>
-      </c>
-      <c r="M8" s="31" t="n">
+        <v>5005</v>
+      </c>
+      <c r="M8" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N8" s="30" t="b">
+      <c r="N8" s="34" t="b">
         <f aca="false">L8&lt;=M8</f>
         <v>1</v>
       </c>
-      <c r="O8" s="31" t="n">
+      <c r="O8" s="35" t="n">
         <f aca="false">ABS(M8-L8)</f>
-        <v>3795.264</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="33" t="n">
         <f aca="false">IF($A9=0,0,$A9*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A9)</f>
         <v>359.37</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="33" t="n">
         <f aca="false">MIN(B9,FarmerHours)</f>
         <v>359.37</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="33" t="n">
         <f aca="false">MAX(B9-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -2657,60 +2803,60 @@
         <f aca="false">IF(D9=0,0,ROUNDUP(D9/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F9" s="30" t="b">
+      <c r="F9" s="34" t="b">
         <f aca="false">AND(B9&lt;=MaxLaborCapacity,E9&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G9" s="31" t="n">
+      <c r="G9" s="35" t="n">
         <f aca="false">C9*FarmerRate</f>
-        <v>12477.3264</v>
-      </c>
-      <c r="H9" s="31" t="n">
+        <v>12478.125</v>
+      </c>
+      <c r="H9" s="35" t="n">
         <f aca="false">D9*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I9" s="31" t="n">
+      <c r="I9" s="35" t="n">
         <f aca="false">$A9*Tom_Fert</f>
         <v>2640</v>
       </c>
-      <c r="J9" s="31" t="n">
+      <c r="J9" s="35" t="n">
         <f aca="false">G9+H9</f>
-        <v>12477.3264</v>
-      </c>
-      <c r="K9" s="31" t="n">
+        <v>12478.125</v>
+      </c>
+      <c r="K9" s="35" t="n">
         <f aca="false">FixedCosts+I9+J9</f>
-        <v>35117.3264</v>
-      </c>
-      <c r="L9" s="31" t="n">
+        <v>35118.125</v>
+      </c>
+      <c r="L9" s="35" t="n">
         <f aca="false">K9-K8</f>
-        <v>5795.3104</v>
-      </c>
-      <c r="M9" s="31" t="n">
+        <v>5795.625</v>
+      </c>
+      <c r="M9" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N9" s="30" t="b">
+      <c r="N9" s="34" t="b">
         <f aca="false">L9&lt;=M9</f>
         <v>1</v>
       </c>
-      <c r="O9" s="31" t="n">
+      <c r="O9" s="35" t="n">
         <f aca="false">ABS(M9-L9)</f>
-        <v>3004.6896</v>
+        <v>3004.375</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="29" t="n">
+      <c r="B10" s="33" t="n">
         <f aca="false">IF($A10=0,0,$A10*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A10)</f>
         <v>527.076</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="33" t="n">
         <f aca="false">MIN(B10,FarmerHours)</f>
         <v>527.076</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="33" t="n">
         <f aca="false">MAX(B10-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -2718,60 +2864,60 @@
         <f aca="false">IF(D10=0,0,ROUNDUP(D10/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F10" s="30" t="b">
+      <c r="F10" s="34" t="b">
         <f aca="false">AND(B10&lt;=MaxLaborCapacity,E10&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G10" s="31" t="n">
+      <c r="G10" s="35" t="n">
         <f aca="false">C10*FarmerRate</f>
-        <v>18300.07872</v>
-      </c>
-      <c r="H10" s="31" t="n">
+        <v>18301.25</v>
+      </c>
+      <c r="H10" s="35" t="n">
         <f aca="false">D10*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I10" s="31" t="n">
+      <c r="I10" s="35" t="n">
         <f aca="false">$A10*Tom_Fert</f>
         <v>3520</v>
       </c>
-      <c r="J10" s="31" t="n">
+      <c r="J10" s="35" t="n">
         <f aca="false">G10+H10</f>
-        <v>18300.07872</v>
-      </c>
-      <c r="K10" s="31" t="n">
+        <v>18301.25</v>
+      </c>
+      <c r="K10" s="35" t="n">
         <f aca="false">FixedCosts+I10+J10</f>
-        <v>41820.07872</v>
-      </c>
-      <c r="L10" s="31" t="n">
+        <v>41821.25</v>
+      </c>
+      <c r="L10" s="35" t="n">
         <f aca="false">K10-K9</f>
-        <v>6702.75232</v>
-      </c>
-      <c r="M10" s="31" t="n">
+        <v>6703.125</v>
+      </c>
+      <c r="M10" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N10" s="30" t="b">
+      <c r="N10" s="34" t="b">
         <f aca="false">L10&lt;=M10</f>
         <v>1</v>
       </c>
-      <c r="O10" s="31" t="n">
+      <c r="O10" s="35" t="n">
         <f aca="false">ABS(M10-L10)</f>
-        <v>2097.24768</v>
+        <v>2096.875</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="29" t="n">
+      <c r="B11" s="33" t="n">
         <f aca="false">IF($A11=0,0,$A11*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A11)</f>
         <v>724.7295</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="33" t="n">
         <f aca="false">MIN(B11,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="33" t="n">
         <f aca="false">MAX(B11-FarmerHours,0)</f>
         <v>4.72950000000026</v>
       </c>
@@ -2779,60 +2925,60 @@
         <f aca="false">IF(D11=0,0,ROUNDUP(D11/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F11" s="30" t="b">
+      <c r="F11" s="34" t="b">
         <f aca="false">AND(B11&lt;=MaxLaborCapacity,E11&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G11" s="31" t="n">
+      <c r="G11" s="35" t="n">
         <f aca="false">C11*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H11" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H11" s="35" t="n">
         <f aca="false">D11*TempRate</f>
-        <v>82.1041200000045</v>
-      </c>
-      <c r="I11" s="31" t="n">
+        <v>82.1093750000045</v>
+      </c>
+      <c r="I11" s="35" t="n">
         <f aca="false">$A11*Tom_Fert</f>
         <v>4400</v>
       </c>
-      <c r="J11" s="31" t="n">
+      <c r="J11" s="35" t="n">
         <f aca="false">G11+H11</f>
-        <v>25080.50412</v>
-      </c>
-      <c r="K11" s="31" t="n">
+        <v>25082.109375</v>
+      </c>
+      <c r="K11" s="35" t="n">
         <f aca="false">FixedCosts+I11+J11</f>
-        <v>49480.50412</v>
-      </c>
-      <c r="L11" s="31" t="n">
+        <v>49482.109375</v>
+      </c>
+      <c r="L11" s="35" t="n">
         <f aca="false">K11-K10</f>
-        <v>7660.42539999999</v>
-      </c>
-      <c r="M11" s="31" t="n">
+        <v>7660.859375</v>
+      </c>
+      <c r="M11" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N11" s="30" t="b">
+      <c r="N11" s="34" t="b">
         <f aca="false">L11&lt;=M11</f>
         <v>1</v>
       </c>
-      <c r="O11" s="31" t="n">
+      <c r="O11" s="35" t="n">
         <f aca="false">ABS(M11-L11)</f>
-        <v>1139.57460000001</v>
+        <v>1139.140625</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="29" t="n">
+      <c r="B12" s="33" t="n">
         <f aca="false">IF($A12=0,0,$A12*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A12)</f>
         <v>956.64294</v>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="33" t="n">
         <f aca="false">MIN(B12,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="33" t="n">
         <f aca="false">MAX(B12-FarmerHours,0)</f>
         <v>236.64294</v>
       </c>
@@ -2840,60 +2986,60 @@
         <f aca="false">IF(D12=0,0,ROUNDUP(D12/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F12" s="30" t="b">
+      <c r="F12" s="34" t="b">
         <f aca="false">AND(B12&lt;=MaxLaborCapacity,E12&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G12" s="31" t="n">
+      <c r="G12" s="35" t="n">
         <f aca="false">C12*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H12" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H12" s="35" t="n">
         <f aca="false">D12*TempRate</f>
-        <v>4108.12143840001</v>
-      </c>
-      <c r="I12" s="31" t="n">
+        <v>4108.38437500001</v>
+      </c>
+      <c r="I12" s="35" t="n">
         <f aca="false">$A12*Tom_Fert</f>
         <v>5280</v>
       </c>
-      <c r="J12" s="31" t="n">
+      <c r="J12" s="35" t="n">
         <f aca="false">G12+H12</f>
-        <v>29106.5214384</v>
-      </c>
-      <c r="K12" s="31" t="n">
+        <v>29108.384375</v>
+      </c>
+      <c r="K12" s="35" t="n">
         <f aca="false">FixedCosts+I12+J12</f>
-        <v>54386.5214384</v>
-      </c>
-      <c r="L12" s="31" t="n">
+        <v>54388.384375</v>
+      </c>
+      <c r="L12" s="35" t="n">
         <f aca="false">K12-K11</f>
-        <v>4906.01731840001</v>
-      </c>
-      <c r="M12" s="31" t="n">
+        <v>4906.27500000001</v>
+      </c>
+      <c r="M12" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N12" s="30" t="b">
+      <c r="N12" s="34" t="b">
         <f aca="false">L12&lt;=M12</f>
         <v>1</v>
       </c>
-      <c r="O12" s="31" t="n">
+      <c r="O12" s="35" t="n">
         <f aca="false">ABS(M12-L12)</f>
-        <v>3893.98268159999</v>
+        <v>3893.72499999999</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="33" t="n">
         <f aca="false">IF($A13=0,0,$A13*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A13)</f>
         <v>1227.691773</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="33" t="n">
         <f aca="false">MIN(B13,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="33" t="n">
         <f aca="false">MAX(B13-FarmerHours,0)</f>
         <v>507.691773000001</v>
       </c>
@@ -2901,60 +3047,60 @@
         <f aca="false">IF(D13=0,0,ROUNDUP(D13/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F13" s="30" t="b">
+      <c r="F13" s="34" t="b">
         <f aca="false">AND(B13&lt;=MaxLaborCapacity,E13&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G13" s="31" t="n">
+      <c r="G13" s="35" t="n">
         <f aca="false">C13*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H13" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H13" s="35" t="n">
         <f aca="false">D13*TempRate</f>
-        <v>8813.52917928001</v>
-      </c>
-      <c r="I13" s="31" t="n">
+        <v>8814.09328125001</v>
+      </c>
+      <c r="I13" s="35" t="n">
         <f aca="false">$A13*Tom_Fert</f>
         <v>6160</v>
       </c>
-      <c r="J13" s="31" t="n">
+      <c r="J13" s="35" t="n">
         <f aca="false">G13+H13</f>
-        <v>33811.92917928</v>
-      </c>
-      <c r="K13" s="31" t="n">
+        <v>33814.09328125</v>
+      </c>
+      <c r="K13" s="35" t="n">
         <f aca="false">FixedCosts+I13+J13</f>
-        <v>59971.92917928</v>
-      </c>
-      <c r="L13" s="31" t="n">
+        <v>59974.09328125</v>
+      </c>
+      <c r="L13" s="35" t="n">
         <f aca="false">K13-K12</f>
-        <v>5585.40774088</v>
-      </c>
-      <c r="M13" s="31" t="n">
+        <v>5585.70890625</v>
+      </c>
+      <c r="M13" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N13" s="30" t="b">
+      <c r="N13" s="34" t="b">
         <f aca="false">L13&lt;=M13</f>
         <v>1</v>
       </c>
-      <c r="O13" s="31" t="n">
+      <c r="O13" s="35" t="n">
         <f aca="false">ABS(M13-L13)</f>
-        <v>3214.59225912</v>
+        <v>3214.29109375</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="29" t="n">
+      <c r="B14" s="33" t="n">
         <f aca="false">IF($A14=0,0,$A14*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A14)</f>
         <v>1543.3839432</v>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="33" t="n">
         <f aca="false">MIN(B14,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="33" t="n">
         <f aca="false">MAX(B14-FarmerHours,0)</f>
         <v>823.383943200001</v>
       </c>
@@ -2962,60 +3108,60 @@
         <f aca="false">IF(D14=0,0,ROUNDUP(D14/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F14" s="30" t="b">
+      <c r="F14" s="34" t="b">
         <f aca="false">AND(B14&lt;=MaxLaborCapacity,E14&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G14" s="31" t="n">
+      <c r="G14" s="35" t="n">
         <f aca="false">C14*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H14" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H14" s="35" t="n">
         <f aca="false">D14*TempRate</f>
-        <v>14293.945253952</v>
-      </c>
-      <c r="I14" s="31" t="n">
+        <v>14294.860125</v>
+      </c>
+      <c r="I14" s="35" t="n">
         <f aca="false">$A14*Tom_Fert</f>
         <v>7040</v>
       </c>
-      <c r="J14" s="31" t="n">
+      <c r="J14" s="35" t="n">
         <f aca="false">G14+H14</f>
-        <v>39292.345253952</v>
-      </c>
-      <c r="K14" s="31" t="n">
+        <v>39294.860125</v>
+      </c>
+      <c r="K14" s="35" t="n">
         <f aca="false">FixedCosts+I14+J14</f>
-        <v>66332.345253952</v>
-      </c>
-      <c r="L14" s="31" t="n">
+        <v>66334.860125</v>
+      </c>
+      <c r="L14" s="35" t="n">
         <f aca="false">K14-K13</f>
-        <v>6360.41607467202</v>
-      </c>
-      <c r="M14" s="31" t="n">
+        <v>6360.76684375001</v>
+      </c>
+      <c r="M14" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N14" s="30" t="b">
+      <c r="N14" s="34" t="b">
         <f aca="false">L14&lt;=M14</f>
         <v>1</v>
       </c>
-      <c r="O14" s="31" t="n">
+      <c r="O14" s="35" t="n">
         <f aca="false">ABS(M14-L14)</f>
-        <v>2439.58392532798</v>
+        <v>2439.23315624999</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="33" t="n">
         <f aca="false">IF($A15=0,0,$A15*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A15)</f>
         <v>1909.93762971</v>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="33" t="n">
         <f aca="false">MIN(B15,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="33" t="n">
         <f aca="false">MAX(B15-FarmerHours,0)</f>
         <v>1189.93762971</v>
       </c>
@@ -3023,60 +3169,60 @@
         <f aca="false">IF(D15=0,0,ROUNDUP(D15/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F15" s="30" t="b">
+      <c r="F15" s="34" t="b">
         <f aca="false">AND(B15&lt;=MaxLaborCapacity,E15&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G15" s="31" t="n">
+      <c r="G15" s="35" t="n">
         <f aca="false">C15*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H15" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H15" s="35" t="n">
         <f aca="false">D15*TempRate</f>
-        <v>20657.3172517656</v>
-      </c>
-      <c r="I15" s="31" t="n">
+        <v>20658.6394046875</v>
+      </c>
+      <c r="I15" s="35" t="n">
         <f aca="false">$A15*Tom_Fert</f>
         <v>7920</v>
       </c>
-      <c r="J15" s="31" t="n">
+      <c r="J15" s="35" t="n">
         <f aca="false">G15+H15</f>
-        <v>45655.7172517656</v>
-      </c>
-      <c r="K15" s="31" t="n">
+        <v>45658.6394046875</v>
+      </c>
+      <c r="K15" s="35" t="n">
         <f aca="false">FixedCosts+I15+J15</f>
-        <v>73575.7172517656</v>
-      </c>
-      <c r="L15" s="31" t="n">
+        <v>73578.6394046875</v>
+      </c>
+      <c r="L15" s="35" t="n">
         <f aca="false">K15-K14</f>
-        <v>7243.37199781361</v>
-      </c>
-      <c r="M15" s="31" t="n">
+        <v>7243.77927968752</v>
+      </c>
+      <c r="M15" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N15" s="30" t="b">
+      <c r="N15" s="34" t="b">
         <f aca="false">L15&lt;=M15</f>
         <v>1</v>
       </c>
-      <c r="O15" s="31" t="n">
+      <c r="O15" s="35" t="n">
         <f aca="false">ABS(M15-L15)</f>
-        <v>1556.62800218639</v>
+        <v>1556.22072031249</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="33" t="n">
         <f aca="false">IF($A16=0,0,$A16*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A16)</f>
         <v>2334.36821409</v>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="33" t="n">
         <f aca="false">MIN(B16,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="33" t="n">
         <f aca="false">MAX(B16-FarmerHours,0)</f>
         <v>1614.36821409</v>
       </c>
@@ -3084,60 +3230,60 @@
         <f aca="false">IF(D16=0,0,ROUNDUP(D16/TempWorkerHours,0))</f>
         <v>2</v>
       </c>
-      <c r="F16" s="30" t="b">
+      <c r="F16" s="34" t="b">
         <f aca="false">AND(B16&lt;=MaxLaborCapacity,E16&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G16" s="31" t="n">
+      <c r="G16" s="35" t="n">
         <f aca="false">C16*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H16" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H16" s="35" t="n">
         <f aca="false">D16*TempRate</f>
-        <v>28025.4321966024</v>
-      </c>
-      <c r="I16" s="31" t="n">
+        <v>28027.2259390625</v>
+      </c>
+      <c r="I16" s="35" t="n">
         <f aca="false">$A16*Tom_Fert</f>
         <v>8800</v>
       </c>
-      <c r="J16" s="31" t="n">
+      <c r="J16" s="35" t="n">
         <f aca="false">G16+H16</f>
-        <v>53023.8321966024</v>
-      </c>
-      <c r="K16" s="31" t="n">
+        <v>53027.2259390625</v>
+      </c>
+      <c r="K16" s="35" t="n">
         <f aca="false">FixedCosts+I16+J16</f>
-        <v>81823.8321966024</v>
-      </c>
-      <c r="L16" s="31" t="n">
+        <v>81827.2259390625</v>
+      </c>
+      <c r="L16" s="35" t="n">
         <f aca="false">K16-K15</f>
-        <v>8248.11494483679</v>
-      </c>
-      <c r="M16" s="31" t="n">
+        <v>8248.58653437501</v>
+      </c>
+      <c r="M16" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N16" s="30" t="b">
+      <c r="N16" s="34" t="b">
         <f aca="false">L16&lt;=M16</f>
         <v>1</v>
       </c>
-      <c r="O16" s="31" t="n">
+      <c r="O16" s="35" t="n">
         <f aca="false">ABS(M16-L16)</f>
-        <v>551.885055163206</v>
+        <v>551.413465624995</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="33" t="n">
         <f aca="false">IF($A17=0,0,$A17*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A17)</f>
         <v>2824.5855390489</v>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="33" t="n">
         <f aca="false">MIN(B17,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="33" t="n">
         <f aca="false">MAX(B17-FarmerHours,0)</f>
         <v>2104.5855390489</v>
       </c>
@@ -3145,60 +3291,60 @@
         <f aca="false">IF(D17=0,0,ROUNDUP(D17/TempWorkerHours,0))</f>
         <v>2</v>
       </c>
-      <c r="F17" s="30" t="b">
+      <c r="F17" s="34" t="b">
         <f aca="false">AND(B17&lt;=MaxLaborCapacity,E17&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G17" s="31" t="n">
+      <c r="G17" s="35" t="n">
         <f aca="false">C17*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H17" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H17" s="35" t="n">
         <f aca="false">D17*TempRate</f>
-        <v>36535.6049578889</v>
-      </c>
-      <c r="I17" s="31" t="n">
+        <v>36537.9433862657</v>
+      </c>
+      <c r="I17" s="35" t="n">
         <f aca="false">$A17*Tom_Fert</f>
         <v>9680</v>
       </c>
-      <c r="J17" s="31" t="n">
+      <c r="J17" s="35" t="n">
         <f aca="false">G17+H17</f>
-        <v>61534.0049578889</v>
-      </c>
-      <c r="K17" s="31" t="n">
+        <v>61537.9433862657</v>
+      </c>
+      <c r="K17" s="35" t="n">
         <f aca="false">FixedCosts+I17+J17</f>
-        <v>91214.0049578889</v>
-      </c>
-      <c r="L17" s="31" t="n">
+        <v>91217.9433862657</v>
+      </c>
+      <c r="L17" s="35" t="n">
         <f aca="false">K17-K16</f>
-        <v>9390.17276128652</v>
-      </c>
-      <c r="M17" s="31" t="n">
+        <v>9390.71744720312</v>
+      </c>
+      <c r="M17" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N17" s="30" t="b">
+      <c r="N17" s="34" t="b">
         <f aca="false">L17&lt;=M17</f>
         <v>0</v>
       </c>
-      <c r="O17" s="31" t="n">
+      <c r="O17" s="35" t="n">
         <f aca="false">ABS(M17-L17)</f>
-        <v>590.172761286522</v>
+        <v>590.717447203118</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="29" t="n">
+      <c r="B18" s="33" t="n">
         <f aca="false">IF($A18=0,0,$A18*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A18)</f>
         <v>3389.50264685868</v>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="33" t="n">
         <f aca="false">MIN(B18,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="33" t="n">
         <f aca="false">MAX(B18-FarmerHours,0)</f>
         <v>2669.50264685868</v>
       </c>
@@ -3206,60 +3352,60 @@
         <f aca="false">IF(D18=0,0,ROUNDUP(D18/TempWorkerHours,0))</f>
         <v>2</v>
       </c>
-      <c r="F18" s="30" t="b">
+      <c r="F18" s="34" t="b">
         <f aca="false">AND(B18&lt;=MaxLaborCapacity,E18&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G18" s="31" t="n">
+      <c r="G18" s="35" t="n">
         <f aca="false">C18*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H18" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H18" s="35" t="n">
         <f aca="false">D18*TempRate</f>
-        <v>46342.5659494667</v>
-      </c>
-      <c r="I18" s="31" t="n">
+        <v>46345.5320635188</v>
+      </c>
+      <c r="I18" s="35" t="n">
         <f aca="false">$A18*Tom_Fert</f>
         <v>10560</v>
       </c>
-      <c r="J18" s="31" t="n">
+      <c r="J18" s="35" t="n">
         <f aca="false">G18+H18</f>
-        <v>71340.9659494667</v>
-      </c>
-      <c r="K18" s="31" t="n">
+        <v>71345.5320635188</v>
+      </c>
+      <c r="K18" s="35" t="n">
         <f aca="false">FixedCosts+I18+J18</f>
-        <v>101900.965949467</v>
-      </c>
-      <c r="L18" s="31" t="n">
+        <v>101905.532063519</v>
+      </c>
+      <c r="L18" s="35" t="n">
         <f aca="false">K18-K17</f>
-        <v>10686.9609915778</v>
-      </c>
-      <c r="M18" s="31" t="n">
+        <v>10687.5886772532</v>
+      </c>
+      <c r="M18" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N18" s="30" t="b">
+      <c r="N18" s="34" t="b">
         <f aca="false">L18&lt;=M18</f>
         <v>0</v>
       </c>
-      <c r="O18" s="31" t="n">
+      <c r="O18" s="35" t="n">
         <f aca="false">ABS(M18-L18)</f>
-        <v>1886.9609915778</v>
+        <v>1887.58867725315</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="33" t="n">
         <f aca="false">IF($A19=0,0,$A19*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A19)</f>
         <v>4039.15732083993</v>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="33" t="n">
         <f aca="false">MIN(B19,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="33" t="n">
         <f aca="false">MAX(B19-FarmerHours,0)</f>
         <v>3319.15732083993</v>
       </c>
@@ -3267,60 +3413,60 @@
         <f aca="false">IF(D19=0,0,ROUNDUP(D19/TempWorkerHours,0))</f>
         <v>3</v>
       </c>
-      <c r="F19" s="30" t="b">
+      <c r="F19" s="34" t="b">
         <f aca="false">AND(B19&lt;=MaxLaborCapacity,E19&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G19" s="31" t="n">
+      <c r="G19" s="35" t="n">
         <f aca="false">C19*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H19" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H19" s="35" t="n">
         <f aca="false">D19*TempRate</f>
-        <v>57620.5710897812</v>
-      </c>
-      <c r="I19" s="31" t="n">
+        <v>57624.2590423599</v>
+      </c>
+      <c r="I19" s="35" t="n">
         <f aca="false">$A19*Tom_Fert</f>
         <v>11440</v>
       </c>
-      <c r="J19" s="31" t="n">
+      <c r="J19" s="35" t="n">
         <f aca="false">G19+H19</f>
-        <v>82618.9710897812</v>
-      </c>
-      <c r="K19" s="31" t="n">
+        <v>82624.2590423599</v>
+      </c>
+      <c r="K19" s="35" t="n">
         <f aca="false">FixedCosts+I19+J19</f>
-        <v>114058.971089781</v>
-      </c>
-      <c r="L19" s="31" t="n">
+        <v>114064.25904236</v>
+      </c>
+      <c r="L19" s="35" t="n">
         <f aca="false">K19-K18</f>
-        <v>12158.0051403145</v>
-      </c>
-      <c r="M19" s="31" t="n">
+        <v>12158.7269788411</v>
+      </c>
+      <c r="M19" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N19" s="30" t="b">
+      <c r="N19" s="34" t="b">
         <f aca="false">L19&lt;=M19</f>
         <v>0</v>
       </c>
-      <c r="O19" s="31" t="n">
+      <c r="O19" s="35" t="n">
         <f aca="false">ABS(M19-L19)</f>
-        <v>3358.00514031446</v>
+        <v>3358.72697884111</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="29" t="n">
+      <c r="B20" s="33" t="n">
         <f aca="false">IF($A20=0,0,$A20*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A20)</f>
         <v>4784.84790314884</v>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="33" t="n">
         <f aca="false">MIN(B20,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="33" t="n">
         <f aca="false">MAX(B20-FarmerHours,0)</f>
         <v>4064.84790314884</v>
       </c>
@@ -3328,60 +3474,60 @@
         <f aca="false">IF(D20=0,0,ROUNDUP(D20/TempWorkerHours,0))</f>
         <v>3</v>
       </c>
-      <c r="F20" s="30" t="b">
+      <c r="F20" s="34" t="b">
         <f aca="false">AND(B20&lt;=MaxLaborCapacity,E20&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G20" s="31" t="n">
+      <c r="G20" s="35" t="n">
         <f aca="false">C20*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H20" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H20" s="35" t="n">
         <f aca="false">D20*TempRate</f>
-        <v>70565.7595986639</v>
-      </c>
-      <c r="I20" s="31" t="n">
+        <v>70570.2760963341</v>
+      </c>
+      <c r="I20" s="35" t="n">
         <f aca="false">$A20*Tom_Fert</f>
         <v>12320</v>
       </c>
-      <c r="J20" s="31" t="n">
+      <c r="J20" s="35" t="n">
         <f aca="false">G20+H20</f>
-        <v>95564.1595986639</v>
-      </c>
-      <c r="K20" s="31" t="n">
+        <v>95570.2760963341</v>
+      </c>
+      <c r="K20" s="35" t="n">
         <f aca="false">FixedCosts+I20+J20</f>
-        <v>127884.159598664</v>
-      </c>
-      <c r="L20" s="31" t="n">
+        <v>127890.276096334</v>
+      </c>
+      <c r="L20" s="35" t="n">
         <f aca="false">K20-K19</f>
-        <v>13825.1885088827</v>
-      </c>
-      <c r="M20" s="31" t="n">
+        <v>13826.0170539742</v>
+      </c>
+      <c r="M20" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N20" s="30" t="b">
+      <c r="N20" s="34" t="b">
         <f aca="false">L20&lt;=M20</f>
         <v>0</v>
       </c>
-      <c r="O20" s="31" t="n">
+      <c r="O20" s="35" t="n">
         <f aca="false">ABS(M20-L20)</f>
-        <v>5025.1885088827</v>
+        <v>5026.01705397415</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="29" t="n">
+      <c r="B21" s="33" t="n">
         <f aca="false">IF($A21=0,0,$A21*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A21)</f>
         <v>5639.28502871114</v>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="33" t="n">
         <f aca="false">MIN(B21,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="33" t="n">
         <f aca="false">MAX(B21-FarmerHours,0)</f>
         <v>4919.28502871114</v>
       </c>
@@ -3389,60 +3535,60 @@
         <f aca="false">IF(D21=0,0,ROUNDUP(D21/TempWorkerHours,0))</f>
         <v>4</v>
       </c>
-      <c r="F21" s="30" t="b">
+      <c r="F21" s="34" t="b">
         <f aca="false">AND(B21&lt;=MaxLaborCapacity,E21&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G21" s="31" t="n">
+      <c r="G21" s="35" t="n">
         <f aca="false">C21*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H21" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H21" s="35" t="n">
         <f aca="false">D21*TempRate</f>
-        <v>85398.7880984253</v>
-      </c>
-      <c r="I21" s="31" t="n">
+        <v>85404.2539706795</v>
+      </c>
+      <c r="I21" s="35" t="n">
         <f aca="false">$A21*Tom_Fert</f>
         <v>13200</v>
       </c>
-      <c r="J21" s="31" t="n">
+      <c r="J21" s="35" t="n">
         <f aca="false">G21+H21</f>
-        <v>110397.188098425</v>
-      </c>
-      <c r="K21" s="31" t="n">
+        <v>110404.253970679</v>
+      </c>
+      <c r="K21" s="35" t="n">
         <f aca="false">FixedCosts+I21+J21</f>
-        <v>143597.188098425</v>
-      </c>
-      <c r="L21" s="31" t="n">
+        <v>143604.253970679</v>
+      </c>
+      <c r="L21" s="35" t="n">
         <f aca="false">K21-K20</f>
-        <v>15713.0284997614</v>
-      </c>
-      <c r="M21" s="31" t="n">
+        <v>15713.9778743454</v>
+      </c>
+      <c r="M21" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N21" s="30" t="b">
+      <c r="N21" s="34" t="b">
         <f aca="false">L21&lt;=M21</f>
         <v>0</v>
       </c>
-      <c r="O21" s="31" t="n">
+      <c r="O21" s="35" t="n">
         <f aca="false">ABS(M21-L21)</f>
-        <v>6913.02849976141</v>
+        <v>6913.97787434538</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="29" t="n">
+      <c r="B22" s="33" t="n">
         <f aca="false">IF($A22=0,0,$A22*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A22)</f>
         <v>6616.7611003544</v>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="33" t="n">
         <f aca="false">MIN(B22,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="33" t="n">
         <f aca="false">MAX(B22-FarmerHours,0)</f>
         <v>5896.7611003544</v>
       </c>
@@ -3450,60 +3596,60 @@
         <f aca="false">IF(D22=0,0,ROUNDUP(D22/TempWorkerHours,0))</f>
         <v>5</v>
       </c>
-      <c r="F22" s="30" t="b">
+      <c r="F22" s="34" t="b">
         <f aca="false">AND(B22&lt;=MaxLaborCapacity,E22&lt;=MaxTempWorkers)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="31" t="n">
+      <c r="G22" s="35" t="n">
         <f aca="false">C22*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H22" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H22" s="35" t="n">
         <f aca="false">D22*TempRate</f>
-        <v>102367.772702152</v>
-      </c>
-      <c r="I22" s="31" t="n">
+        <v>102374.324658931</v>
+      </c>
+      <c r="I22" s="35" t="n">
         <f aca="false">$A22*Tom_Fert</f>
         <v>14080</v>
       </c>
-      <c r="J22" s="31" t="n">
+      <c r="J22" s="35" t="n">
         <f aca="false">G22+H22</f>
-        <v>127366.172702152</v>
-      </c>
-      <c r="K22" s="31" t="n">
+        <v>127374.324658931</v>
+      </c>
+      <c r="K22" s="35" t="n">
         <f aca="false">FixedCosts+I22+J22</f>
-        <v>161446.172702152</v>
-      </c>
-      <c r="L22" s="31" t="n">
+        <v>161454.324658931</v>
+      </c>
+      <c r="L22" s="35" t="n">
         <f aca="false">K22-K21</f>
-        <v>17848.9846037271</v>
-      </c>
-      <c r="M22" s="31" t="n">
+        <v>17850.0706882511</v>
+      </c>
+      <c r="M22" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N22" s="30" t="b">
+      <c r="N22" s="34" t="b">
         <f aca="false">L22&lt;=M22</f>
         <v>0</v>
       </c>
-      <c r="O22" s="31" t="n">
+      <c r="O22" s="35" t="n">
         <f aca="false">ABS(M22-L22)</f>
-        <v>9048.98460372706</v>
+        <v>9050.07068825109</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="29" t="n">
+      <c r="B23" s="33" t="n">
         <f aca="false">IF($A23=0,0,$A23*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A23)</f>
         <v>7733.33953603921</v>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="33" t="n">
         <f aca="false">MIN(B23,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="33" t="n">
         <f aca="false">MAX(B23-FarmerHours,0)</f>
         <v>7013.33953603921</v>
       </c>
@@ -3511,60 +3657,60 @@
         <f aca="false">IF(D23=0,0,ROUNDUP(D23/TempWorkerHours,0))</f>
         <v>5</v>
       </c>
-      <c r="F23" s="30" t="b">
+      <c r="F23" s="34" t="b">
         <f aca="false">AND(B23&lt;=MaxLaborCapacity,E23&lt;=MaxTempWorkers)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="31" t="n">
+      <c r="G23" s="35" t="n">
         <f aca="false">C23*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H23" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H23" s="35" t="n">
         <f aca="false">D23*TempRate</f>
-        <v>121751.574345641</v>
-      </c>
-      <c r="I23" s="31" t="n">
+        <v>121759.366945125</v>
+      </c>
+      <c r="I23" s="35" t="n">
         <f aca="false">$A23*Tom_Fert</f>
         <v>14960</v>
       </c>
-      <c r="J23" s="31" t="n">
+      <c r="J23" s="35" t="n">
         <f aca="false">G23+H23</f>
-        <v>146749.974345641</v>
-      </c>
-      <c r="K23" s="31" t="n">
+        <v>146759.366945125</v>
+      </c>
+      <c r="K23" s="35" t="n">
         <f aca="false">FixedCosts+I23+J23</f>
-        <v>181709.974345641</v>
-      </c>
-      <c r="L23" s="31" t="n">
+        <v>181719.366945125</v>
+      </c>
+      <c r="L23" s="35" t="n">
         <f aca="false">K23-K22</f>
-        <v>20263.8016434882</v>
-      </c>
-      <c r="M23" s="31" t="n">
+        <v>20265.0422861946</v>
+      </c>
+      <c r="M23" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N23" s="30" t="b">
+      <c r="N23" s="34" t="b">
         <f aca="false">L23&lt;=M23</f>
         <v>0</v>
       </c>
-      <c r="O23" s="31" t="n">
+      <c r="O23" s="35" t="n">
         <f aca="false">ABS(M23-L23)</f>
-        <v>11463.8016434882</v>
+        <v>11465.0422861946</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="29" t="n">
+      <c r="B24" s="33" t="n">
         <f aca="false">IF($A24=0,0,$A24*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A24)</f>
         <v>9007.06604785743</v>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="33" t="n">
         <f aca="false">MIN(B24,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="33" t="n">
         <f aca="false">MAX(B24-FarmerHours,0)</f>
         <v>8287.06604785743</v>
       </c>
@@ -3572,60 +3718,60 @@
         <f aca="false">IF(D24=0,0,ROUNDUP(D24/TempWorkerHours,0))</f>
         <v>6</v>
       </c>
-      <c r="F24" s="30" t="b">
+      <c r="F24" s="34" t="b">
         <f aca="false">AND(B24&lt;=MaxLaborCapacity,E24&lt;=MaxTempWorkers)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="31" t="n">
+      <c r="G24" s="35" t="n">
         <f aca="false">C24*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H24" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H24" s="35" t="n">
         <f aca="false">D24*TempRate</f>
-        <v>143863.466590805</v>
-      </c>
-      <c r="I24" s="31" t="n">
+        <v>143872.674441969</v>
+      </c>
+      <c r="I24" s="35" t="n">
         <f aca="false">$A24*Tom_Fert</f>
         <v>15840</v>
       </c>
-      <c r="J24" s="31" t="n">
+      <c r="J24" s="35" t="n">
         <f aca="false">G24+H24</f>
-        <v>168861.866590805</v>
-      </c>
-      <c r="K24" s="31" t="n">
+        <v>168872.674441969</v>
+      </c>
+      <c r="K24" s="35" t="n">
         <f aca="false">FixedCosts+I24+J24</f>
-        <v>204701.866590805</v>
-      </c>
-      <c r="L24" s="31" t="n">
+        <v>204712.674441969</v>
+      </c>
+      <c r="L24" s="35" t="n">
         <f aca="false">K24-K23</f>
-        <v>22991.8922451643</v>
-      </c>
-      <c r="M24" s="31" t="n">
+        <v>22993.3074968441</v>
+      </c>
+      <c r="M24" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N24" s="30" t="b">
+      <c r="N24" s="34" t="b">
         <f aca="false">L24&lt;=M24</f>
         <v>0</v>
       </c>
-      <c r="O24" s="31" t="n">
+      <c r="O24" s="35" t="n">
         <f aca="false">ABS(M24-L24)</f>
-        <v>14191.8922451643</v>
+        <v>14193.3074968441</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="29" t="n">
+      <c r="B25" s="33" t="n">
         <f aca="false">IF($A25=0,0,$A25*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A25)</f>
         <v>10458.2044666789</v>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="33" t="n">
         <f aca="false">MIN(B25,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="33" t="n">
         <f aca="false">MAX(B25-FarmerHours,0)</f>
         <v>9738.2044666789</v>
       </c>
@@ -3633,60 +3779,60 @@
         <f aca="false">IF(D25=0,0,ROUNDUP(D25/TempWorkerHours,0))</f>
         <v>7</v>
       </c>
-      <c r="F25" s="30" t="b">
+      <c r="F25" s="34" t="b">
         <f aca="false">AND(B25&lt;=MaxLaborCapacity,E25&lt;=MaxTempWorkers)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="31" t="n">
+      <c r="G25" s="35" t="n">
         <f aca="false">C25*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H25" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H25" s="35" t="n">
         <f aca="false">D25*TempRate</f>
-        <v>169055.229541546</v>
-      </c>
-      <c r="I25" s="31" t="n">
+        <v>169066.049768731</v>
+      </c>
+      <c r="I25" s="35" t="n">
         <f aca="false">$A25*Tom_Fert</f>
         <v>16720</v>
       </c>
-      <c r="J25" s="31" t="n">
+      <c r="J25" s="35" t="n">
         <f aca="false">G25+H25</f>
-        <v>194053.629541546</v>
-      </c>
-      <c r="K25" s="31" t="n">
+        <v>194066.049768731</v>
+      </c>
+      <c r="K25" s="35" t="n">
         <f aca="false">FixedCosts+I25+J25</f>
-        <v>230773.629541546</v>
-      </c>
-      <c r="L25" s="31" t="n">
+        <v>230786.049768731</v>
+      </c>
+      <c r="L25" s="35" t="n">
         <f aca="false">K25-K24</f>
-        <v>26071.7629507408</v>
-      </c>
-      <c r="M25" s="31" t="n">
+        <v>26073.3753267617</v>
+      </c>
+      <c r="M25" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N25" s="30" t="b">
+      <c r="N25" s="34" t="b">
         <f aca="false">L25&lt;=M25</f>
         <v>0</v>
       </c>
-      <c r="O25" s="31" t="n">
+      <c r="O25" s="35" t="n">
         <f aca="false">ABS(M25-L25)</f>
-        <v>17271.7629507408</v>
+        <v>17273.3753267617</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="29" t="n">
+      <c r="B26" s="33" t="n">
         <f aca="false">IF($A26=0,0,$A26*Tom_BaseLabor*SeasonLength*(1+Tom_DR)^$A26)</f>
         <v>12109.4999087861</v>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="33" t="n">
         <f aca="false">MIN(B26,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="33" t="n">
         <f aca="false">MAX(B26-FarmerHours,0)</f>
         <v>11389.4999087861</v>
       </c>
@@ -3694,45 +3840,45 @@
         <f aca="false">IF(D26=0,0,ROUNDUP(D26/TempWorkerHours,0))</f>
         <v>8</v>
       </c>
-      <c r="F26" s="30" t="b">
+      <c r="F26" s="34" t="b">
         <f aca="false">AND(B26&lt;=MaxLaborCapacity,E26&lt;=MaxTempWorkers)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="31" t="n">
+      <c r="G26" s="35" t="n">
         <f aca="false">C26*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H26" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H26" s="35" t="n">
         <f aca="false">D26*TempRate</f>
-        <v>197721.718416527</v>
-      </c>
-      <c r="I26" s="31" t="n">
+        <v>197734.373416425</v>
+      </c>
+      <c r="I26" s="35" t="n">
         <f aca="false">$A26*Tom_Fert</f>
         <v>17600</v>
       </c>
-      <c r="J26" s="31" t="n">
+      <c r="J26" s="35" t="n">
         <f aca="false">G26+H26</f>
-        <v>222720.118416527</v>
-      </c>
-      <c r="K26" s="31" t="n">
+        <v>222734.373416425</v>
+      </c>
+      <c r="K26" s="35" t="n">
         <f aca="false">FixedCosts+I26+J26</f>
-        <v>260320.118416527</v>
-      </c>
-      <c r="L26" s="31" t="n">
+        <v>260334.373416425</v>
+      </c>
+      <c r="L26" s="35" t="n">
         <f aca="false">K26-K25</f>
-        <v>29546.4888749809</v>
-      </c>
-      <c r="M26" s="31" t="n">
+        <v>29548.3236476944</v>
+      </c>
+      <c r="M26" s="35" t="n">
         <f aca="false">Tom_Rev</f>
         <v>8800</v>
       </c>
-      <c r="N26" s="30" t="b">
+      <c r="N26" s="34" t="b">
         <f aca="false">L26&lt;=M26</f>
         <v>0</v>
       </c>
-      <c r="O26" s="31" t="n">
+      <c r="O26" s="35" t="n">
         <f aca="false">ABS(M26-L26)</f>
-        <v>20746.4888749809</v>
+        <v>20748.3236476944</v>
       </c>
     </row>
   </sheetData>
@@ -3804,7 +3950,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3823,7 +3969,7 @@
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -3842,64 +3988,64 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>69</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>74</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>76</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="29" t="n">
+      <c r="B6" s="33" t="n">
         <f aca="false">IF($A6=0,0,$A6*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A6)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="33" t="n">
         <f aca="false">MIN(B6,FarmerHours)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="33" t="n">
         <f aca="false">MAX(B6-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -3907,51 +4053,51 @@
         <f aca="false">IF(D6=0,0,ROUNDUP(D6/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F6" s="30" t="b">
+      <c r="F6" s="34" t="b">
         <f aca="false">AND(B6&lt;=MaxLaborCapacity,E6&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G6" s="31" t="n">
+      <c r="G6" s="35" t="n">
         <f aca="false">C6*FarmerRate</f>
         <v>0</v>
       </c>
-      <c r="H6" s="31" t="n">
+      <c r="H6" s="35" t="n">
         <f aca="false">D6*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I6" s="31" t="n">
+      <c r="I6" s="35" t="n">
         <f aca="false">$A6*Car_Fert</f>
         <v>0</v>
       </c>
-      <c r="J6" s="31" t="n">
+      <c r="J6" s="35" t="n">
         <f aca="false">G6+H6</f>
         <v>0</v>
       </c>
-      <c r="K6" s="31" t="n">
+      <c r="K6" s="35" t="n">
         <f aca="false">FixedCosts+I6+J6</f>
         <v>20000</v>
       </c>
-      <c r="L6" s="32"/>
-      <c r="M6" s="31" t="n">
+      <c r="L6" s="36"/>
+      <c r="M6" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N6" s="32"/>
-      <c r="O6" s="32"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="33" t="n">
         <f aca="false">IF($A7=0,0,$A7*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A7)</f>
-        <v>30.7377</v>
-      </c>
-      <c r="C7" s="29" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="C7" s="33" t="n">
         <f aca="false">MIN(B7,FarmerHours)</f>
-        <v>30.7377</v>
-      </c>
-      <c r="D7" s="29" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="D7" s="33" t="n">
         <f aca="false">MAX(B7-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -3959,60 +4105,60 @@
         <f aca="false">IF(D7=0,0,ROUNDUP(D7/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F7" s="30" t="b">
+      <c r="F7" s="34" t="b">
         <f aca="false">AND(B7&lt;=MaxLaborCapacity,E7&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G7" s="31" t="n">
+      <c r="G7" s="35" t="n">
         <f aca="false">C7*FarmerRate</f>
-        <v>1067.212944</v>
-      </c>
-      <c r="H7" s="31" t="n">
+        <v>1067.70833333333</v>
+      </c>
+      <c r="H7" s="35" t="n">
         <f aca="false">D7*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I7" s="31" t="n">
+      <c r="I7" s="35" t="n">
         <f aca="false">$A7*Car_Fert</f>
         <v>440</v>
       </c>
-      <c r="J7" s="31" t="n">
+      <c r="J7" s="35" t="n">
         <f aca="false">G7+H7</f>
-        <v>1067.212944</v>
-      </c>
-      <c r="K7" s="31" t="n">
+        <v>1067.70833333333</v>
+      </c>
+      <c r="K7" s="35" t="n">
         <f aca="false">FixedCosts+I7+J7</f>
-        <v>21507.212944</v>
-      </c>
-      <c r="L7" s="31" t="n">
+        <v>21507.7083333333</v>
+      </c>
+      <c r="L7" s="35" t="n">
         <f aca="false">K7-K6</f>
-        <v>1507.212944</v>
-      </c>
-      <c r="M7" s="31" t="n">
+        <v>1507.70833333333</v>
+      </c>
+      <c r="M7" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N7" s="30" t="b">
+      <c r="N7" s="34" t="b">
         <f aca="false">L7&lt;=M7</f>
         <v>1</v>
       </c>
-      <c r="O7" s="31" t="n">
+      <c r="O7" s="35" t="n">
         <f aca="false">ABS(M7-L7)</f>
-        <v>586.787056000001</v>
+        <v>586.291666666668</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="33" t="n">
         <f aca="false">IF($A8=0,0,$A8*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A8)</f>
-        <v>63.012285</v>
-      </c>
-      <c r="C8" s="29" t="n">
+        <v>63.0375</v>
+      </c>
+      <c r="C8" s="33" t="n">
         <f aca="false">MIN(B8,FarmerHours)</f>
-        <v>63.012285</v>
-      </c>
-      <c r="D8" s="29" t="n">
+        <v>63.0375</v>
+      </c>
+      <c r="D8" s="33" t="n">
         <f aca="false">MAX(B8-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -4020,60 +4166,60 @@
         <f aca="false">IF(D8=0,0,ROUNDUP(D8/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F8" s="30" t="b">
+      <c r="F8" s="34" t="b">
         <f aca="false">AND(B8&lt;=MaxLaborCapacity,E8&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G8" s="31" t="n">
+      <c r="G8" s="35" t="n">
         <f aca="false">C8*FarmerRate</f>
-        <v>2187.7865352</v>
-      </c>
-      <c r="H8" s="31" t="n">
+        <v>2188.80208333333</v>
+      </c>
+      <c r="H8" s="35" t="n">
         <f aca="false">D8*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I8" s="31" t="n">
+      <c r="I8" s="35" t="n">
         <f aca="false">$A8*Car_Fert</f>
         <v>880</v>
       </c>
-      <c r="J8" s="31" t="n">
+      <c r="J8" s="35" t="n">
         <f aca="false">G8+H8</f>
-        <v>2187.7865352</v>
-      </c>
-      <c r="K8" s="31" t="n">
+        <v>2188.80208333333</v>
+      </c>
+      <c r="K8" s="35" t="n">
         <f aca="false">FixedCosts+I8+J8</f>
-        <v>23067.7865352</v>
-      </c>
-      <c r="L8" s="31" t="n">
+        <v>23068.8020833333</v>
+      </c>
+      <c r="L8" s="35" t="n">
         <f aca="false">K8-K7</f>
-        <v>1560.5735912</v>
-      </c>
-      <c r="M8" s="31" t="n">
+        <v>1561.09375</v>
+      </c>
+      <c r="M8" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N8" s="30" t="b">
+      <c r="N8" s="34" t="b">
         <f aca="false">L8&lt;=M8</f>
         <v>1</v>
       </c>
-      <c r="O8" s="31" t="n">
+      <c r="O8" s="35" t="n">
         <f aca="false">ABS(M8-L8)</f>
-        <v>533.426408799998</v>
+        <v>532.90625</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="33" t="n">
         <f aca="false">IF($A9=0,0,$A9*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A9)</f>
-        <v>96.8813881875</v>
-      </c>
-      <c r="C9" s="29" t="n">
+        <v>96.92015625</v>
+      </c>
+      <c r="C9" s="33" t="n">
         <f aca="false">MIN(B9,FarmerHours)</f>
-        <v>96.8813881875</v>
-      </c>
-      <c r="D9" s="29" t="n">
+        <v>96.92015625</v>
+      </c>
+      <c r="D9" s="33" t="n">
         <f aca="false">MAX(B9-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -4081,60 +4227,60 @@
         <f aca="false">IF(D9=0,0,ROUNDUP(D9/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F9" s="30" t="b">
+      <c r="F9" s="34" t="b">
         <f aca="false">AND(B9&lt;=MaxLaborCapacity,E9&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G9" s="31" t="n">
+      <c r="G9" s="35" t="n">
         <f aca="false">C9*FarmerRate</f>
-        <v>3363.72179787</v>
-      </c>
-      <c r="H9" s="31" t="n">
+        <v>3365.283203125</v>
+      </c>
+      <c r="H9" s="35" t="n">
         <f aca="false">D9*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I9" s="31" t="n">
+      <c r="I9" s="35" t="n">
         <f aca="false">$A9*Car_Fert</f>
         <v>1320</v>
       </c>
-      <c r="J9" s="31" t="n">
+      <c r="J9" s="35" t="n">
         <f aca="false">G9+H9</f>
-        <v>3363.72179787</v>
-      </c>
-      <c r="K9" s="31" t="n">
+        <v>3365.283203125</v>
+      </c>
+      <c r="K9" s="35" t="n">
         <f aca="false">FixedCosts+I9+J9</f>
-        <v>24683.72179787</v>
-      </c>
-      <c r="L9" s="31" t="n">
+        <v>24685.283203125</v>
+      </c>
+      <c r="L9" s="35" t="n">
         <f aca="false">K9-K8</f>
-        <v>1615.93526267</v>
-      </c>
-      <c r="M9" s="31" t="n">
+        <v>1616.48111979167</v>
+      </c>
+      <c r="M9" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N9" s="30" t="b">
+      <c r="N9" s="34" t="b">
         <f aca="false">L9&lt;=M9</f>
         <v>1</v>
       </c>
-      <c r="O9" s="31" t="n">
+      <c r="O9" s="35" t="n">
         <f aca="false">ABS(M9-L9)</f>
-        <v>478.064737330002</v>
+        <v>477.518880208332</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="29" t="n">
+      <c r="B10" s="33" t="n">
         <f aca="false">IF($A10=0,0,$A10*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A10)</f>
-        <v>132.40456385625</v>
-      </c>
-      <c r="C10" s="29" t="n">
+        <v>132.457546875</v>
+      </c>
+      <c r="C10" s="33" t="n">
         <f aca="false">MIN(B10,FarmerHours)</f>
-        <v>132.40456385625</v>
-      </c>
-      <c r="D10" s="29" t="n">
+        <v>132.457546875</v>
+      </c>
+      <c r="D10" s="33" t="n">
         <f aca="false">MAX(B10-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -4142,60 +4288,60 @@
         <f aca="false">IF(D10=0,0,ROUNDUP(D10/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F10" s="30" t="b">
+      <c r="F10" s="34" t="b">
         <f aca="false">AND(B10&lt;=MaxLaborCapacity,E10&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G10" s="31" t="n">
+      <c r="G10" s="35" t="n">
         <f aca="false">C10*FarmerRate</f>
-        <v>4597.086457089</v>
-      </c>
-      <c r="H10" s="31" t="n">
+        <v>4599.22037760416</v>
+      </c>
+      <c r="H10" s="35" t="n">
         <f aca="false">D10*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I10" s="31" t="n">
+      <c r="I10" s="35" t="n">
         <f aca="false">$A10*Car_Fert</f>
         <v>1760</v>
       </c>
-      <c r="J10" s="31" t="n">
+      <c r="J10" s="35" t="n">
         <f aca="false">G10+H10</f>
-        <v>4597.086457089</v>
-      </c>
-      <c r="K10" s="31" t="n">
+        <v>4599.22037760416</v>
+      </c>
+      <c r="K10" s="35" t="n">
         <f aca="false">FixedCosts+I10+J10</f>
-        <v>26357.086457089</v>
-      </c>
-      <c r="L10" s="31" t="n">
+        <v>26359.2203776042</v>
+      </c>
+      <c r="L10" s="35" t="n">
         <f aca="false">K10-K9</f>
-        <v>1673.364659219</v>
-      </c>
-      <c r="M10" s="31" t="n">
+        <v>1673.93717447916</v>
+      </c>
+      <c r="M10" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N10" s="30" t="b">
+      <c r="N10" s="34" t="b">
         <f aca="false">L10&lt;=M10</f>
         <v>1</v>
       </c>
-      <c r="O10" s="31" t="n">
+      <c r="O10" s="35" t="n">
         <f aca="false">ABS(M10-L10)</f>
-        <v>420.635340781002</v>
+        <v>420.062825520836</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="29" t="n">
+      <c r="B11" s="33" t="n">
         <f aca="false">IF($A11=0,0,$A11*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A11)</f>
-        <v>169.64334744082</v>
-      </c>
-      <c r="C11" s="29" t="n">
+        <v>169.711231933594</v>
+      </c>
+      <c r="C11" s="33" t="n">
         <f aca="false">MIN(B11,FarmerHours)</f>
-        <v>169.64334744082</v>
-      </c>
-      <c r="D11" s="29" t="n">
+        <v>169.711231933594</v>
+      </c>
+      <c r="D11" s="33" t="n">
         <f aca="false">MAX(B11-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -4203,60 +4349,60 @@
         <f aca="false">IF(D11=0,0,ROUNDUP(D11/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F11" s="30" t="b">
+      <c r="F11" s="34" t="b">
         <f aca="false">AND(B11&lt;=MaxLaborCapacity,E11&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G11" s="31" t="n">
+      <c r="G11" s="35" t="n">
         <f aca="false">C11*FarmerRate</f>
-        <v>5890.01702314528</v>
-      </c>
-      <c r="H11" s="31" t="n">
+        <v>5892.75110880534</v>
+      </c>
+      <c r="H11" s="35" t="n">
         <f aca="false">D11*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I11" s="31" t="n">
+      <c r="I11" s="35" t="n">
         <f aca="false">$A11*Car_Fert</f>
         <v>2200</v>
       </c>
-      <c r="J11" s="31" t="n">
+      <c r="J11" s="35" t="n">
         <f aca="false">G11+H11</f>
-        <v>5890.01702314528</v>
-      </c>
-      <c r="K11" s="31" t="n">
+        <v>5892.75110880534</v>
+      </c>
+      <c r="K11" s="35" t="n">
         <f aca="false">FixedCosts+I11+J11</f>
-        <v>28090.0170231453</v>
-      </c>
-      <c r="L11" s="31" t="n">
+        <v>28092.7511088053</v>
+      </c>
+      <c r="L11" s="35" t="n">
         <f aca="false">K11-K10</f>
-        <v>1732.93056605628</v>
-      </c>
-      <c r="M11" s="31" t="n">
+        <v>1733.53073120117</v>
+      </c>
+      <c r="M11" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N11" s="30" t="b">
+      <c r="N11" s="34" t="b">
         <f aca="false">L11&lt;=M11</f>
         <v>1</v>
       </c>
-      <c r="O11" s="31" t="n">
+      <c r="O11" s="35" t="n">
         <f aca="false">ABS(M11-L11)</f>
-        <v>361.069433943718</v>
+        <v>360.469268798828</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="29" t="n">
+      <c r="B12" s="33" t="n">
         <f aca="false">IF($A12=0,0,$A12*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A12)</f>
-        <v>208.661317352209</v>
-      </c>
-      <c r="C12" s="29" t="n">
+        <v>208.74481527832</v>
+      </c>
+      <c r="C12" s="33" t="n">
         <f aca="false">MIN(B12,FarmerHours)</f>
-        <v>208.661317352209</v>
-      </c>
-      <c r="D12" s="29" t="n">
+        <v>208.74481527832</v>
+      </c>
+      <c r="D12" s="33" t="n">
         <f aca="false">MAX(B12-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -4264,60 +4410,60 @@
         <f aca="false">IF(D12=0,0,ROUNDUP(D12/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F12" s="30" t="b">
+      <c r="F12" s="34" t="b">
         <f aca="false">AND(B12&lt;=MaxLaborCapacity,E12&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G12" s="31" t="n">
+      <c r="G12" s="35" t="n">
         <f aca="false">C12*FarmerRate</f>
-        <v>7244.72093846869</v>
-      </c>
-      <c r="H12" s="31" t="n">
+        <v>7248.08386383056</v>
+      </c>
+      <c r="H12" s="35" t="n">
         <f aca="false">D12*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I12" s="31" t="n">
+      <c r="I12" s="35" t="n">
         <f aca="false">$A12*Car_Fert</f>
         <v>2640</v>
       </c>
-      <c r="J12" s="31" t="n">
+      <c r="J12" s="35" t="n">
         <f aca="false">G12+H12</f>
-        <v>7244.72093846869</v>
-      </c>
-      <c r="K12" s="31" t="n">
+        <v>7248.08386383056</v>
+      </c>
+      <c r="K12" s="35" t="n">
         <f aca="false">FixedCosts+I12+J12</f>
-        <v>29884.7209384687</v>
-      </c>
-      <c r="L12" s="31" t="n">
+        <v>29888.0838638306</v>
+      </c>
+      <c r="L12" s="35" t="n">
         <f aca="false">K12-K11</f>
-        <v>1794.70391532341</v>
-      </c>
-      <c r="M12" s="31" t="n">
+        <v>1795.33275502523</v>
+      </c>
+      <c r="M12" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N12" s="30" t="b">
+      <c r="N12" s="34" t="b">
         <f aca="false">L12&lt;=M12</f>
         <v>1</v>
       </c>
-      <c r="O12" s="31" t="n">
+      <c r="O12" s="35" t="n">
         <f aca="false">ABS(M12-L12)</f>
-        <v>299.296084676589</v>
+        <v>298.667244974775</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="33" t="n">
         <f aca="false">IF($A13=0,0,$A13*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A13)</f>
-        <v>249.524158667016</v>
-      </c>
-      <c r="C13" s="29" t="n">
+        <v>249.624008270325</v>
+      </c>
+      <c r="C13" s="33" t="n">
         <f aca="false">MIN(B13,FarmerHours)</f>
-        <v>249.524158667016</v>
-      </c>
-      <c r="D13" s="29" t="n">
+        <v>249.624008270325</v>
+      </c>
+      <c r="D13" s="33" t="n">
         <f aca="false">MAX(B13-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -4325,60 +4471,60 @@
         <f aca="false">IF(D13=0,0,ROUNDUP(D13/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F13" s="30" t="b">
+      <c r="F13" s="34" t="b">
         <f aca="false">AND(B13&lt;=MaxLaborCapacity,E13&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G13" s="31" t="n">
+      <c r="G13" s="35" t="n">
         <f aca="false">C13*FarmerRate</f>
-        <v>8663.47878891881</v>
-      </c>
-      <c r="H13" s="31" t="n">
+        <v>8667.50028716405</v>
+      </c>
+      <c r="H13" s="35" t="n">
         <f aca="false">D13*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I13" s="31" t="n">
+      <c r="I13" s="35" t="n">
         <f aca="false">$A13*Car_Fert</f>
         <v>3080</v>
       </c>
-      <c r="J13" s="31" t="n">
+      <c r="J13" s="35" t="n">
         <f aca="false">G13+H13</f>
-        <v>8663.47878891881</v>
-      </c>
-      <c r="K13" s="31" t="n">
+        <v>8667.50028716405</v>
+      </c>
+      <c r="K13" s="35" t="n">
         <f aca="false">FixedCosts+I13+J13</f>
-        <v>31743.4787889188</v>
-      </c>
-      <c r="L13" s="31" t="n">
+        <v>31747.5002871641</v>
+      </c>
+      <c r="L13" s="35" t="n">
         <f aca="false">K13-K12</f>
-        <v>1858.75785045012</v>
-      </c>
-      <c r="M13" s="31" t="n">
+        <v>1859.41642333349</v>
+      </c>
+      <c r="M13" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N13" s="30" t="b">
+      <c r="N13" s="34" t="b">
         <f aca="false">L13&lt;=M13</f>
         <v>1</v>
       </c>
-      <c r="O13" s="31" t="n">
+      <c r="O13" s="35" t="n">
         <f aca="false">ABS(M13-L13)</f>
-        <v>235.242149549882</v>
+        <v>234.583576666511</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="29" t="n">
+      <c r="B14" s="33" t="n">
         <f aca="false">IF($A14=0,0,$A14*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A14)</f>
-        <v>292.299728724219</v>
-      </c>
-      <c r="C14" s="29" t="n">
+        <v>292.41669540238</v>
+      </c>
+      <c r="C14" s="33" t="n">
         <f aca="false">MIN(B14,FarmerHours)</f>
-        <v>292.299728724219</v>
-      </c>
-      <c r="D14" s="29" t="n">
+        <v>292.41669540238</v>
+      </c>
+      <c r="D14" s="33" t="n">
         <f aca="false">MAX(B14-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -4386,60 +4532,60 @@
         <f aca="false">IF(D14=0,0,ROUNDUP(D14/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F14" s="30" t="b">
+      <c r="F14" s="34" t="b">
         <f aca="false">AND(B14&lt;=MaxLaborCapacity,E14&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G14" s="31" t="n">
+      <c r="G14" s="35" t="n">
         <f aca="false">C14*FarmerRate</f>
-        <v>10148.6465813049</v>
-      </c>
-      <c r="H14" s="31" t="n">
+        <v>10153.3574792493</v>
+      </c>
+      <c r="H14" s="35" t="n">
         <f aca="false">D14*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I14" s="31" t="n">
+      <c r="I14" s="35" t="n">
         <f aca="false">$A14*Car_Fert</f>
         <v>3520</v>
       </c>
-      <c r="J14" s="31" t="n">
+      <c r="J14" s="35" t="n">
         <f aca="false">G14+H14</f>
-        <v>10148.6465813049</v>
-      </c>
-      <c r="K14" s="31" t="n">
+        <v>10153.3574792493</v>
+      </c>
+      <c r="K14" s="35" t="n">
         <f aca="false">FixedCosts+I14+J14</f>
-        <v>33668.6465813049</v>
-      </c>
-      <c r="L14" s="31" t="n">
+        <v>33673.3574792493</v>
+      </c>
+      <c r="L14" s="35" t="n">
         <f aca="false">K14-K13</f>
-        <v>1925.16779238608</v>
-      </c>
-      <c r="M14" s="31" t="n">
+        <v>1925.85719208526</v>
+      </c>
+      <c r="M14" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N14" s="30" t="b">
+      <c r="N14" s="34" t="b">
         <f aca="false">L14&lt;=M14</f>
         <v>1</v>
       </c>
-      <c r="O14" s="31" t="n">
+      <c r="O14" s="35" t="n">
         <f aca="false">ABS(M14-L14)</f>
-        <v>168.832207613923</v>
+        <v>168.142807914741</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="33" t="n">
         <f aca="false">IF($A15=0,0,$A15*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A15)</f>
-        <v>337.058124685115</v>
-      </c>
-      <c r="C15" s="29" t="n">
+        <v>337.19300188587</v>
+      </c>
+      <c r="C15" s="33" t="n">
         <f aca="false">MIN(B15,FarmerHours)</f>
-        <v>337.058124685115</v>
-      </c>
-      <c r="D15" s="29" t="n">
+        <v>337.19300188587</v>
+      </c>
+      <c r="D15" s="33" t="n">
         <f aca="false">MAX(B15-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -4447,60 +4593,60 @@
         <f aca="false">IF(D15=0,0,ROUNDUP(D15/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F15" s="30" t="b">
+      <c r="F15" s="34" t="b">
         <f aca="false">AND(B15&lt;=MaxLaborCapacity,E15&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G15" s="31" t="n">
+      <c r="G15" s="35" t="n">
         <f aca="false">C15*FarmerRate</f>
-        <v>11702.6580890672</v>
-      </c>
-      <c r="H15" s="31" t="n">
+        <v>11708.0903432594</v>
+      </c>
+      <c r="H15" s="35" t="n">
         <f aca="false">D15*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I15" s="31" t="n">
+      <c r="I15" s="35" t="n">
         <f aca="false">$A15*Car_Fert</f>
         <v>3960</v>
       </c>
-      <c r="J15" s="31" t="n">
+      <c r="J15" s="35" t="n">
         <f aca="false">G15+H15</f>
-        <v>11702.6580890672</v>
-      </c>
-      <c r="K15" s="31" t="n">
+        <v>11708.0903432594</v>
+      </c>
+      <c r="K15" s="35" t="n">
         <f aca="false">FixedCosts+I15+J15</f>
-        <v>35662.6580890672</v>
-      </c>
-      <c r="L15" s="31" t="n">
+        <v>35668.0903432594</v>
+      </c>
+      <c r="L15" s="35" t="n">
         <f aca="false">K15-K14</f>
-        <v>1994.01150776232</v>
-      </c>
-      <c r="M15" s="31" t="n">
+        <v>1994.73286401005</v>
+      </c>
+      <c r="M15" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N15" s="30" t="b">
+      <c r="N15" s="34" t="b">
         <f aca="false">L15&lt;=M15</f>
         <v>1</v>
       </c>
-      <c r="O15" s="31" t="n">
+      <c r="O15" s="35" t="n">
         <f aca="false">ABS(M15-L15)</f>
-        <v>99.9884922376805</v>
+        <v>99.2671359899468</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="33" t="n">
         <f aca="false">IF($A16=0,0,$A16*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A16)</f>
-        <v>383.871753113603</v>
-      </c>
-      <c r="C16" s="29" t="n">
+        <v>384.025363258907</v>
+      </c>
+      <c r="C16" s="33" t="n">
         <f aca="false">MIN(B16,FarmerHours)</f>
-        <v>383.871753113603</v>
-      </c>
-      <c r="D16" s="29" t="n">
+        <v>384.025363258907</v>
+      </c>
+      <c r="D16" s="33" t="n">
         <f aca="false">MAX(B16-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -4508,60 +4654,60 @@
         <f aca="false">IF(D16=0,0,ROUNDUP(D16/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F16" s="30" t="b">
+      <c r="F16" s="34" t="b">
         <f aca="false">AND(B16&lt;=MaxLaborCapacity,E16&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G16" s="31" t="n">
+      <c r="G16" s="35" t="n">
         <f aca="false">C16*FarmerRate</f>
-        <v>13328.0272681043</v>
-      </c>
-      <c r="H16" s="31" t="n">
+        <v>13334.2140020454</v>
+      </c>
+      <c r="H16" s="35" t="n">
         <f aca="false">D16*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I16" s="31" t="n">
+      <c r="I16" s="35" t="n">
         <f aca="false">$A16*Car_Fert</f>
         <v>4400</v>
       </c>
-      <c r="J16" s="31" t="n">
+      <c r="J16" s="35" t="n">
         <f aca="false">G16+H16</f>
-        <v>13328.0272681043</v>
-      </c>
-      <c r="K16" s="31" t="n">
+        <v>13334.2140020454</v>
+      </c>
+      <c r="K16" s="35" t="n">
         <f aca="false">FixedCosts+I16+J16</f>
-        <v>37728.0272681043</v>
-      </c>
-      <c r="L16" s="31" t="n">
+        <v>37734.2140020454</v>
+      </c>
+      <c r="L16" s="35" t="n">
         <f aca="false">K16-K15</f>
-        <v>2065.36917903711</v>
-      </c>
-      <c r="M16" s="31" t="n">
+        <v>2066.12365878602</v>
+      </c>
+      <c r="M16" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N16" s="30" t="b">
+      <c r="N16" s="34" t="b">
         <f aca="false">L16&lt;=M16</f>
         <v>1</v>
       </c>
-      <c r="O16" s="31" t="n">
+      <c r="O16" s="35" t="n">
         <f aca="false">ABS(M16-L16)</f>
-        <v>28.6308209628915</v>
+        <v>27.8763412139815</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="33" t="n">
         <f aca="false">IF($A17=0,0,$A17*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A17)</f>
-        <v>432.815401635588</v>
-      </c>
-      <c r="C17" s="29" t="n">
+        <v>432.988597074418</v>
+      </c>
+      <c r="C17" s="33" t="n">
         <f aca="false">MIN(B17,FarmerHours)</f>
-        <v>432.815401635588</v>
-      </c>
-      <c r="D17" s="29" t="n">
+        <v>432.988597074418</v>
+      </c>
+      <c r="D17" s="33" t="n">
         <f aca="false">MAX(B17-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -4569,60 +4715,60 @@
         <f aca="false">IF(D17=0,0,ROUNDUP(D17/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F17" s="30" t="b">
+      <c r="F17" s="34" t="b">
         <f aca="false">AND(B17&lt;=MaxLaborCapacity,E17&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G17" s="31" t="n">
+      <c r="G17" s="35" t="n">
         <f aca="false">C17*FarmerRate</f>
-        <v>15027.3507447876</v>
-      </c>
-      <c r="H17" s="31" t="n">
+        <v>15034.3262873062</v>
+      </c>
+      <c r="H17" s="35" t="n">
         <f aca="false">D17*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I17" s="31" t="n">
+      <c r="I17" s="35" t="n">
         <f aca="false">$A17*Car_Fert</f>
         <v>4840</v>
       </c>
-      <c r="J17" s="31" t="n">
+      <c r="J17" s="35" t="n">
         <f aca="false">G17+H17</f>
-        <v>15027.3507447876</v>
-      </c>
-      <c r="K17" s="31" t="n">
+        <v>15034.3262873062</v>
+      </c>
+      <c r="K17" s="35" t="n">
         <f aca="false">FixedCosts+I17+J17</f>
-        <v>39867.3507447876</v>
-      </c>
-      <c r="L17" s="31" t="n">
+        <v>39874.3262873062</v>
+      </c>
+      <c r="L17" s="35" t="n">
         <f aca="false">K17-K16</f>
-        <v>2139.3234766833</v>
-      </c>
-      <c r="M17" s="31" t="n">
+        <v>2140.11228526079</v>
+      </c>
+      <c r="M17" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N17" s="30" t="b">
+      <c r="N17" s="34" t="b">
         <f aca="false">L17&lt;=M17</f>
         <v>0</v>
       </c>
-      <c r="O17" s="31" t="n">
+      <c r="O17" s="35" t="n">
         <f aca="false">ABS(M17-L17)</f>
-        <v>45.3234766832975</v>
+        <v>46.1122852607878</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="29" t="n">
+      <c r="B18" s="33" t="n">
         <f aca="false">IF($A18=0,0,$A18*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A18)</f>
-        <v>483.966312737975</v>
-      </c>
-      <c r="C18" s="29" t="n">
+        <v>484.159976728667</v>
+      </c>
+      <c r="C18" s="33" t="n">
         <f aca="false">MIN(B18,FarmerHours)</f>
-        <v>483.966312737975</v>
-      </c>
-      <c r="D18" s="29" t="n">
+        <v>484.159976728667</v>
+      </c>
+      <c r="D18" s="33" t="n">
         <f aca="false">MAX(B18-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -4630,60 +4776,60 @@
         <f aca="false">IF(D18=0,0,ROUNDUP(D18/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F18" s="30" t="b">
+      <c r="F18" s="34" t="b">
         <f aca="false">AND(B18&lt;=MaxLaborCapacity,E18&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G18" s="31" t="n">
+      <c r="G18" s="35" t="n">
         <f aca="false">C18*FarmerRate</f>
-        <v>16803.3103782625</v>
-      </c>
-      <c r="H18" s="31" t="n">
+        <v>16811.1103030787</v>
+      </c>
+      <c r="H18" s="35" t="n">
         <f aca="false">D18*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I18" s="31" t="n">
+      <c r="I18" s="35" t="n">
         <f aca="false">$A18*Car_Fert</f>
         <v>5280</v>
       </c>
-      <c r="J18" s="31" t="n">
+      <c r="J18" s="35" t="n">
         <f aca="false">G18+H18</f>
-        <v>16803.3103782625</v>
-      </c>
-      <c r="K18" s="31" t="n">
+        <v>16811.1103030787</v>
+      </c>
+      <c r="K18" s="35" t="n">
         <f aca="false">FixedCosts+I18+J18</f>
-        <v>42083.3103782625</v>
-      </c>
-      <c r="L18" s="31" t="n">
+        <v>42091.1103030787</v>
+      </c>
+      <c r="L18" s="35" t="n">
         <f aca="false">K18-K17</f>
-        <v>2215.95963347489</v>
-      </c>
-      <c r="M18" s="31" t="n">
+        <v>2216.78401577254</v>
+      </c>
+      <c r="M18" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N18" s="30" t="b">
+      <c r="N18" s="34" t="b">
         <f aca="false">L18&lt;=M18</f>
         <v>0</v>
       </c>
-      <c r="O18" s="31" t="n">
+      <c r="O18" s="35" t="n">
         <f aca="false">ABS(M18-L18)</f>
-        <v>121.959633474893</v>
+        <v>122.784015772544</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="33" t="n">
         <f aca="false">IF($A19=0,0,$A19*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A19)</f>
-        <v>537.40425976946</v>
-      </c>
-      <c r="C19" s="29" t="n">
+        <v>537.619307492457</v>
+      </c>
+      <c r="C19" s="33" t="n">
         <f aca="false">MIN(B19,FarmerHours)</f>
-        <v>537.40425976946</v>
-      </c>
-      <c r="D19" s="29" t="n">
+        <v>537.619307492457</v>
+      </c>
+      <c r="D19" s="33" t="n">
         <f aca="false">MAX(B19-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -4691,60 +4837,60 @@
         <f aca="false">IF(D19=0,0,ROUNDUP(D19/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F19" s="30" t="b">
+      <c r="F19" s="34" t="b">
         <f aca="false">AND(B19&lt;=MaxLaborCapacity,E19&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G19" s="31" t="n">
+      <c r="G19" s="35" t="n">
         <f aca="false">C19*FarmerRate</f>
-        <v>18658.6758991957</v>
-      </c>
-      <c r="H19" s="31" t="n">
+        <v>18667.3370657103</v>
+      </c>
+      <c r="H19" s="35" t="n">
         <f aca="false">D19*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I19" s="31" t="n">
+      <c r="I19" s="35" t="n">
         <f aca="false">$A19*Car_Fert</f>
         <v>5720</v>
       </c>
-      <c r="J19" s="31" t="n">
+      <c r="J19" s="35" t="n">
         <f aca="false">G19+H19</f>
-        <v>18658.6758991957</v>
-      </c>
-      <c r="K19" s="31" t="n">
+        <v>18667.3370657103</v>
+      </c>
+      <c r="K19" s="35" t="n">
         <f aca="false">FixedCosts+I19+J19</f>
-        <v>44378.6758991957</v>
-      </c>
-      <c r="L19" s="31" t="n">
+        <v>44387.3370657103</v>
+      </c>
+      <c r="L19" s="35" t="n">
         <f aca="false">K19-K18</f>
-        <v>2295.36552093315</v>
-      </c>
-      <c r="M19" s="31" t="n">
+        <v>2296.2267626316</v>
+      </c>
+      <c r="M19" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N19" s="30" t="b">
+      <c r="N19" s="34" t="b">
         <f aca="false">L19&lt;=M19</f>
         <v>0</v>
       </c>
-      <c r="O19" s="31" t="n">
+      <c r="O19" s="35" t="n">
         <f aca="false">ABS(M19-L19)</f>
-        <v>201.365520933148</v>
+        <v>202.226762631602</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="29" t="n">
+      <c r="B20" s="33" t="n">
         <f aca="false">IF($A20=0,0,$A20*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A20)</f>
-        <v>593.211625207058</v>
-      </c>
-      <c r="C20" s="29" t="n">
+        <v>593.449004808982</v>
+      </c>
+      <c r="C20" s="33" t="n">
         <f aca="false">MIN(B20,FarmerHours)</f>
-        <v>593.211625207058</v>
-      </c>
-      <c r="D20" s="29" t="n">
+        <v>593.449004808982</v>
+      </c>
+      <c r="D20" s="33" t="n">
         <f aca="false">MAX(B20-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -4752,60 +4898,60 @@
         <f aca="false">IF(D20=0,0,ROUNDUP(D20/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F20" s="30" t="b">
+      <c r="F20" s="34" t="b">
         <f aca="false">AND(B20&lt;=MaxLaborCapacity,E20&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G20" s="31" t="n">
+      <c r="G20" s="35" t="n">
         <f aca="false">C20*FarmerRate</f>
-        <v>20596.3076271891</v>
-      </c>
-      <c r="H20" s="31" t="n">
+        <v>20605.8682225341</v>
+      </c>
+      <c r="H20" s="35" t="n">
         <f aca="false">D20*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I20" s="31" t="n">
+      <c r="I20" s="35" t="n">
         <f aca="false">$A20*Car_Fert</f>
         <v>6160</v>
       </c>
-      <c r="J20" s="31" t="n">
+      <c r="J20" s="35" t="n">
         <f aca="false">G20+H20</f>
-        <v>20596.3076271891</v>
-      </c>
-      <c r="K20" s="31" t="n">
+        <v>20605.8682225341</v>
+      </c>
+      <c r="K20" s="35" t="n">
         <f aca="false">FixedCosts+I20+J20</f>
-        <v>46756.3076271891</v>
-      </c>
-      <c r="L20" s="31" t="n">
+        <v>46765.8682225341</v>
+      </c>
+      <c r="L20" s="35" t="n">
         <f aca="false">K20-K19</f>
-        <v>2377.6317279934</v>
-      </c>
-      <c r="M20" s="31" t="n">
+        <v>2378.53115682377</v>
+      </c>
+      <c r="M20" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N20" s="30" t="b">
+      <c r="N20" s="34" t="b">
         <f aca="false">L20&lt;=M20</f>
         <v>0</v>
       </c>
-      <c r="O20" s="31" t="n">
+      <c r="O20" s="35" t="n">
         <f aca="false">ABS(M20-L20)</f>
-        <v>283.631727993401</v>
+        <v>284.531156823767</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="29" t="n">
+      <c r="B21" s="33" t="n">
         <f aca="false">IF($A21=0,0,$A21*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A21)</f>
-        <v>651.47348125418</v>
-      </c>
-      <c r="C21" s="29" t="n">
+        <v>651.734174924149</v>
+      </c>
+      <c r="C21" s="33" t="n">
         <f aca="false">MIN(B21,FarmerHours)</f>
-        <v>651.47348125418</v>
-      </c>
-      <c r="D21" s="29" t="n">
+        <v>651.734174924149</v>
+      </c>
+      <c r="D21" s="33" t="n">
         <f aca="false">MAX(B21-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -4813,60 +4959,60 @@
         <f aca="false">IF(D21=0,0,ROUNDUP(D21/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F21" s="30" t="b">
+      <c r="F21" s="34" t="b">
         <f aca="false">AND(B21&lt;=MaxLaborCapacity,E21&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G21" s="31" t="n">
+      <c r="G21" s="35" t="n">
         <f aca="false">C21*FarmerRate</f>
-        <v>22619.1592691451</v>
-      </c>
-      <c r="H21" s="31" t="n">
+        <v>22629.658851533</v>
+      </c>
+      <c r="H21" s="35" t="n">
         <f aca="false">D21*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I21" s="31" t="n">
+      <c r="I21" s="35" t="n">
         <f aca="false">$A21*Car_Fert</f>
         <v>6600</v>
       </c>
-      <c r="J21" s="31" t="n">
+      <c r="J21" s="35" t="n">
         <f aca="false">G21+H21</f>
-        <v>22619.1592691451</v>
-      </c>
-      <c r="K21" s="31" t="n">
+        <v>22629.658851533</v>
+      </c>
+      <c r="K21" s="35" t="n">
         <f aca="false">FixedCosts+I21+J21</f>
-        <v>49219.1592691451</v>
-      </c>
-      <c r="L21" s="31" t="n">
+        <v>49229.658851533</v>
+      </c>
+      <c r="L21" s="35" t="n">
         <f aca="false">K21-K20</f>
-        <v>2462.85164195607</v>
-      </c>
-      <c r="M21" s="31" t="n">
+        <v>2463.79062899888</v>
+      </c>
+      <c r="M21" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N21" s="30" t="b">
+      <c r="N21" s="34" t="b">
         <f aca="false">L21&lt;=M21</f>
         <v>0</v>
       </c>
-      <c r="O21" s="31" t="n">
+      <c r="O21" s="35" t="n">
         <f aca="false">ABS(M21-L21)</f>
-        <v>368.851641956069</v>
+        <v>369.790628998882</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="29" t="n">
+      <c r="B22" s="33" t="n">
         <f aca="false">IF($A22=0,0,$A22*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A22)</f>
-        <v>712.277672837903</v>
-      </c>
-      <c r="C22" s="29" t="n">
+        <v>712.56269791707</v>
+      </c>
+      <c r="C22" s="33" t="n">
         <f aca="false">MIN(B22,FarmerHours)</f>
-        <v>712.277672837903</v>
-      </c>
-      <c r="D22" s="29" t="n">
+        <v>712.56269791707</v>
+      </c>
+      <c r="D22" s="33" t="n">
         <f aca="false">MAX(B22-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -4874,289 +5020,289 @@
         <f aca="false">IF(D22=0,0,ROUNDUP(D22/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F22" s="30" t="b">
+      <c r="F22" s="34" t="b">
         <f aca="false">AND(B22&lt;=MaxLaborCapacity,E22&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G22" s="31" t="n">
+      <c r="G22" s="35" t="n">
         <f aca="false">C22*FarmerRate</f>
-        <v>24730.280800932</v>
-      </c>
-      <c r="H22" s="31" t="n">
+        <v>24741.7603443427</v>
+      </c>
+      <c r="H22" s="35" t="n">
         <f aca="false">D22*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I22" s="31" t="n">
+      <c r="I22" s="35" t="n">
         <f aca="false">$A22*Car_Fert</f>
         <v>7040</v>
       </c>
-      <c r="J22" s="31" t="n">
+      <c r="J22" s="35" t="n">
         <f aca="false">G22+H22</f>
-        <v>24730.280800932</v>
-      </c>
-      <c r="K22" s="31" t="n">
+        <v>24741.7603443427</v>
+      </c>
+      <c r="K22" s="35" t="n">
         <f aca="false">FixedCosts+I22+J22</f>
-        <v>51770.280800932</v>
-      </c>
-      <c r="L22" s="31" t="n">
+        <v>51781.7603443427</v>
+      </c>
+      <c r="L22" s="35" t="n">
         <f aca="false">K22-K21</f>
-        <v>2551.12153178687</v>
-      </c>
-      <c r="M22" s="31" t="n">
+        <v>2552.10149280974</v>
+      </c>
+      <c r="M22" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N22" s="30" t="b">
+      <c r="N22" s="34" t="b">
         <f aca="false">L22&lt;=M22</f>
         <v>0</v>
       </c>
-      <c r="O22" s="31" t="n">
+      <c r="O22" s="35" t="n">
         <f aca="false">ABS(M22-L22)</f>
-        <v>457.12153178687</v>
+        <v>458.101492809743</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="29" t="n">
+      <c r="B23" s="33" t="n">
         <f aca="false">IF($A23=0,0,$A23*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A23)</f>
-        <v>775.714903075029</v>
-      </c>
-      <c r="C23" s="29" t="n">
+        <v>776.025313200309</v>
+      </c>
+      <c r="C23" s="33" t="n">
         <f aca="false">MIN(B23,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="33" t="n">
         <f aca="false">MAX(B23-FarmerHours,0)</f>
-        <v>55.7149030750287</v>
+        <v>56.0253132003089</v>
       </c>
       <c r="E23" s="12" t="n">
         <f aca="false">IF(D23=0,0,ROUNDUP(D23/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F23" s="30" t="b">
+      <c r="F23" s="34" t="b">
         <f aca="false">AND(B23&lt;=MaxLaborCapacity,E23&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G23" s="31" t="n">
+      <c r="G23" s="35" t="n">
         <f aca="false">C23*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H23" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H23" s="35" t="n">
         <f aca="false">D23*TempRate</f>
-        <v>967.210717382498</v>
-      </c>
-      <c r="I23" s="31" t="n">
+        <v>972.661687505363</v>
+      </c>
+      <c r="I23" s="35" t="n">
         <f aca="false">$A23*Car_Fert</f>
         <v>7480</v>
       </c>
-      <c r="J23" s="31" t="n">
+      <c r="J23" s="35" t="n">
         <f aca="false">G23+H23</f>
-        <v>25965.6107173825</v>
-      </c>
-      <c r="K23" s="31" t="n">
+        <v>25972.6616875054</v>
+      </c>
+      <c r="K23" s="35" t="n">
         <f aca="false">FixedCosts+I23+J23</f>
-        <v>53445.6107173825</v>
-      </c>
-      <c r="L23" s="31" t="n">
+        <v>53452.6616875054</v>
+      </c>
+      <c r="L23" s="35" t="n">
         <f aca="false">K23-K22</f>
-        <v>1675.32991645051</v>
-      </c>
-      <c r="M23" s="31" t="n">
+        <v>1670.90134316265</v>
+      </c>
+      <c r="M23" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N23" s="30" t="b">
+      <c r="N23" s="34" t="b">
         <f aca="false">L23&lt;=M23</f>
         <v>1</v>
       </c>
-      <c r="O23" s="31" t="n">
+      <c r="O23" s="35" t="n">
         <f aca="false">ABS(M23-L23)</f>
-        <v>418.670083549492</v>
+        <v>423.098656837348</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="29" t="n">
+      <c r="B24" s="33" t="n">
         <f aca="false">IF($A24=0,0,$A24*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A24)</f>
-        <v>841.878821278487</v>
-      </c>
-      <c r="C24" s="29" t="n">
+        <v>842.215707561512</v>
+      </c>
+      <c r="C24" s="33" t="n">
         <f aca="false">MIN(B24,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="33" t="n">
         <f aca="false">MAX(B24-FarmerHours,0)</f>
-        <v>121.878821278487</v>
+        <v>122.215707561512</v>
       </c>
       <c r="E24" s="12" t="n">
         <f aca="false">IF(D24=0,0,ROUNDUP(D24/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F24" s="30" t="b">
+      <c r="F24" s="34" t="b">
         <f aca="false">AND(B24&lt;=MaxLaborCapacity,E24&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G24" s="31" t="n">
+      <c r="G24" s="35" t="n">
         <f aca="false">C24*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H24" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H24" s="35" t="n">
         <f aca="false">D24*TempRate</f>
-        <v>2115.81633739453</v>
-      </c>
-      <c r="I24" s="31" t="n">
+        <v>2121.80047849846</v>
+      </c>
+      <c r="I24" s="35" t="n">
         <f aca="false">$A24*Car_Fert</f>
         <v>7920</v>
       </c>
-      <c r="J24" s="31" t="n">
+      <c r="J24" s="35" t="n">
         <f aca="false">G24+H24</f>
-        <v>27114.2163373945</v>
-      </c>
-      <c r="K24" s="31" t="n">
+        <v>27121.8004784985</v>
+      </c>
+      <c r="K24" s="35" t="n">
         <f aca="false">FixedCosts+I24+J24</f>
-        <v>55034.2163373945</v>
-      </c>
-      <c r="L24" s="31" t="n">
+        <v>55041.8004784985</v>
+      </c>
+      <c r="L24" s="35" t="n">
         <f aca="false">K24-K23</f>
-        <v>1588.60562001203</v>
-      </c>
-      <c r="M24" s="31" t="n">
+        <v>1589.13879099311</v>
+      </c>
+      <c r="M24" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N24" s="30" t="b">
+      <c r="N24" s="34" t="b">
         <f aca="false">L24&lt;=M24</f>
         <v>1</v>
       </c>
-      <c r="O24" s="31" t="n">
+      <c r="O24" s="35" t="n">
         <f aca="false">ABS(M24-L24)</f>
-        <v>505.394379987971</v>
+        <v>504.861209006893</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="29" t="n">
+      <c r="B25" s="33" t="n">
         <f aca="false">IF($A25=0,0,$A25*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A25)</f>
-        <v>910.866113577696</v>
-      </c>
-      <c r="C25" s="29" t="n">
+        <v>911.230605820024</v>
+      </c>
+      <c r="C25" s="33" t="n">
         <f aca="false">MIN(B25,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="33" t="n">
         <f aca="false">MAX(B25-FarmerHours,0)</f>
-        <v>190.866113577696</v>
+        <v>191.230605820024</v>
       </c>
       <c r="E25" s="12" t="n">
         <f aca="false">IF(D25=0,0,ROUNDUP(D25/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F25" s="30" t="b">
+      <c r="F25" s="34" t="b">
         <f aca="false">AND(B25&lt;=MaxLaborCapacity,E25&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G25" s="31" t="n">
+      <c r="G25" s="35" t="n">
         <f aca="false">C25*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H25" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H25" s="35" t="n">
         <f aca="false">D25*TempRate</f>
-        <v>3313.43573170881</v>
-      </c>
-      <c r="I25" s="31" t="n">
+        <v>3319.97579548653</v>
+      </c>
+      <c r="I25" s="35" t="n">
         <f aca="false">$A25*Car_Fert</f>
         <v>8360</v>
       </c>
-      <c r="J25" s="31" t="n">
+      <c r="J25" s="35" t="n">
         <f aca="false">G25+H25</f>
-        <v>28311.8357317088</v>
-      </c>
-      <c r="K25" s="31" t="n">
+        <v>28319.9757954865</v>
+      </c>
+      <c r="K25" s="35" t="n">
         <f aca="false">FixedCosts+I25+J25</f>
-        <v>56671.8357317088</v>
-      </c>
-      <c r="L25" s="31" t="n">
+        <v>56679.9757954865</v>
+      </c>
+      <c r="L25" s="35" t="n">
         <f aca="false">K25-K24</f>
-        <v>1637.61939431428</v>
-      </c>
-      <c r="M25" s="31" t="n">
+        <v>1638.17531698807</v>
+      </c>
+      <c r="M25" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N25" s="30" t="b">
+      <c r="N25" s="34" t="b">
         <f aca="false">L25&lt;=M25</f>
         <v>1</v>
       </c>
-      <c r="O25" s="31" t="n">
+      <c r="O25" s="35" t="n">
         <f aca="false">ABS(M25-L25)</f>
-        <v>456.380605685721</v>
+        <v>455.824683011932</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="29" t="n">
+      <c r="B26" s="33" t="n">
         <f aca="false">IF($A26=0,0,$A26*Car_BaseLabor*SeasonLength*(1+Car_DR)^$A26)</f>
-        <v>982.776596228567</v>
-      </c>
-      <c r="C26" s="29" t="n">
+        <v>983.169864174237</v>
+      </c>
+      <c r="C26" s="33" t="n">
         <f aca="false">MIN(B26,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="33" t="n">
         <f aca="false">MAX(B26-FarmerHours,0)</f>
-        <v>262.776596228567</v>
+        <v>263.169864174237</v>
       </c>
       <c r="E26" s="12" t="n">
         <f aca="false">IF(D26=0,0,ROUNDUP(D26/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F26" s="30" t="b">
+      <c r="F26" s="34" t="b">
         <f aca="false">AND(B26&lt;=MaxLaborCapacity,E26&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G26" s="31" t="n">
+      <c r="G26" s="35" t="n">
         <f aca="false">C26*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H26" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H26" s="35" t="n">
         <f aca="false">D26*TempRate</f>
-        <v>4561.80171052792</v>
-      </c>
-      <c r="I26" s="31" t="n">
+        <v>4568.92125302494</v>
+      </c>
+      <c r="I26" s="35" t="n">
         <f aca="false">$A26*Car_Fert</f>
         <v>8800</v>
       </c>
-      <c r="J26" s="31" t="n">
+      <c r="J26" s="35" t="n">
         <f aca="false">G26+H26</f>
-        <v>29560.2017105279</v>
-      </c>
-      <c r="K26" s="31" t="n">
+        <v>29568.9212530249</v>
+      </c>
+      <c r="K26" s="35" t="n">
         <f aca="false">FixedCosts+I26+J26</f>
-        <v>58360.2017105279</v>
-      </c>
-      <c r="L26" s="31" t="n">
+        <v>58368.9212530249</v>
+      </c>
+      <c r="L26" s="35" t="n">
         <f aca="false">K26-K25</f>
-        <v>1688.36597881911</v>
-      </c>
-      <c r="M26" s="31" t="n">
+        <v>1688.9454575384</v>
+      </c>
+      <c r="M26" s="35" t="n">
         <f aca="false">Car_Rev</f>
         <v>2094</v>
       </c>
-      <c r="N26" s="30" t="b">
+      <c r="N26" s="34" t="b">
         <f aca="false">L26&lt;=M26</f>
         <v>1</v>
       </c>
-      <c r="O26" s="31" t="n">
+      <c r="O26" s="35" t="n">
         <f aca="false">ABS(M26-L26)</f>
-        <v>405.634021180886</v>
+        <v>405.054542461599</v>
       </c>
     </row>
   </sheetData>
@@ -5228,7 +5374,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5247,7 +5393,7 @@
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -5266,64 +5412,64 @@
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>69</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>74</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>76</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="29" t="n">
+      <c r="B6" s="33" t="n">
         <f aca="false">IF($A6=0,0,$A6*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A6)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="33" t="n">
         <f aca="false">MIN(B6,FarmerHours)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="33" t="n">
         <f aca="false">MAX(B6-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -5331,51 +5477,51 @@
         <f aca="false">IF(D6=0,0,ROUNDUP(D6/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F6" s="30" t="b">
+      <c r="F6" s="34" t="b">
         <f aca="false">AND(B6&lt;=MaxLaborCapacity,E6&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G6" s="31" t="n">
+      <c r="G6" s="35" t="n">
         <f aca="false">C6*FarmerRate</f>
         <v>0</v>
       </c>
-      <c r="H6" s="31" t="n">
+      <c r="H6" s="35" t="n">
         <f aca="false">D6*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I6" s="31" t="n">
+      <c r="I6" s="35" t="n">
         <f aca="false">$A6*Mes_Fert</f>
         <v>0</v>
       </c>
-      <c r="J6" s="31" t="n">
+      <c r="J6" s="35" t="n">
         <f aca="false">G6+H6</f>
         <v>0</v>
       </c>
-      <c r="K6" s="31" t="n">
+      <c r="K6" s="35" t="n">
         <f aca="false">FixedCosts+I6+J6</f>
         <v>20000</v>
       </c>
-      <c r="L6" s="32"/>
-      <c r="M6" s="31" t="n">
+      <c r="L6" s="36"/>
+      <c r="M6" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N6" s="32"/>
-      <c r="O6" s="32"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="33" t="n">
         <f aca="false">IF($A7=0,0,$A7*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A7)</f>
         <v>45.5625</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="33" t="n">
         <f aca="false">MIN(B7,FarmerHours)</f>
         <v>45.5625</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="33" t="n">
         <f aca="false">MAX(B7-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -5383,60 +5529,60 @@
         <f aca="false">IF(D7=0,0,ROUNDUP(D7/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F7" s="30" t="b">
+      <c r="F7" s="34" t="b">
         <f aca="false">AND(B7&lt;=MaxLaborCapacity,E7&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G7" s="31" t="n">
+      <c r="G7" s="35" t="n">
         <f aca="false">C7*FarmerRate</f>
-        <v>1581.93</v>
-      </c>
-      <c r="H7" s="31" t="n">
+        <v>1582.03125</v>
+      </c>
+      <c r="H7" s="35" t="n">
         <f aca="false">D7*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I7" s="31" t="n">
+      <c r="I7" s="35" t="n">
         <f aca="false">$A7*Mes_Fert</f>
         <v>880</v>
       </c>
-      <c r="J7" s="31" t="n">
+      <c r="J7" s="35" t="n">
         <f aca="false">G7+H7</f>
-        <v>1581.93</v>
-      </c>
-      <c r="K7" s="31" t="n">
+        <v>1582.03125</v>
+      </c>
+      <c r="K7" s="35" t="n">
         <f aca="false">FixedCosts+I7+J7</f>
-        <v>22461.93</v>
-      </c>
-      <c r="L7" s="31" t="n">
+        <v>22462.03125</v>
+      </c>
+      <c r="L7" s="35" t="n">
         <f aca="false">K7-K6</f>
-        <v>2461.93</v>
-      </c>
-      <c r="M7" s="31" t="n">
+        <v>2462.03125</v>
+      </c>
+      <c r="M7" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N7" s="30" t="b">
+      <c r="N7" s="34" t="b">
         <f aca="false">L7&lt;=M7</f>
         <v>1</v>
       </c>
-      <c r="O7" s="31" t="n">
+      <c r="O7" s="35" t="n">
         <f aca="false">ABS(M7-L7)</f>
-        <v>238.07</v>
+        <v>237.96875</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="33" t="n">
         <f aca="false">IF($A8=0,0,$A8*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A8)</f>
         <v>92.2640625</v>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="33" t="n">
         <f aca="false">MIN(B8,FarmerHours)</f>
         <v>92.2640625</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="33" t="n">
         <f aca="false">MAX(B8-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -5444,60 +5590,60 @@
         <f aca="false">IF(D8=0,0,ROUNDUP(D8/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F8" s="30" t="b">
+      <c r="F8" s="34" t="b">
         <f aca="false">AND(B8&lt;=MaxLaborCapacity,E8&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G8" s="31" t="n">
+      <c r="G8" s="35" t="n">
         <f aca="false">C8*FarmerRate</f>
-        <v>3203.40825</v>
-      </c>
-      <c r="H8" s="31" t="n">
+        <v>3203.61328125</v>
+      </c>
+      <c r="H8" s="35" t="n">
         <f aca="false">D8*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I8" s="31" t="n">
+      <c r="I8" s="35" t="n">
         <f aca="false">$A8*Mes_Fert</f>
         <v>1760</v>
       </c>
-      <c r="J8" s="31" t="n">
+      <c r="J8" s="35" t="n">
         <f aca="false">G8+H8</f>
-        <v>3203.40825</v>
-      </c>
-      <c r="K8" s="31" t="n">
+        <v>3203.61328125</v>
+      </c>
+      <c r="K8" s="35" t="n">
         <f aca="false">FixedCosts+I8+J8</f>
-        <v>24963.40825</v>
-      </c>
-      <c r="L8" s="31" t="n">
+        <v>24963.61328125</v>
+      </c>
+      <c r="L8" s="35" t="n">
         <f aca="false">K8-K7</f>
-        <v>2501.47825</v>
-      </c>
-      <c r="M8" s="31" t="n">
+        <v>2501.58203125</v>
+      </c>
+      <c r="M8" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N8" s="30" t="b">
+      <c r="N8" s="34" t="b">
         <f aca="false">L8&lt;=M8</f>
         <v>1</v>
       </c>
-      <c r="O8" s="31" t="n">
+      <c r="O8" s="35" t="n">
         <f aca="false">ABS(M8-L8)</f>
-        <v>198.52175</v>
+        <v>198.41796875</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="33" t="n">
         <f aca="false">IF($A9=0,0,$A9*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A9)</f>
         <v>140.126044921875</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="33" t="n">
         <f aca="false">MIN(B9,FarmerHours)</f>
         <v>140.126044921875</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="33" t="n">
         <f aca="false">MAX(B9-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -5505,60 +5651,60 @@
         <f aca="false">IF(D9=0,0,ROUNDUP(D9/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F9" s="30" t="b">
+      <c r="F9" s="34" t="b">
         <f aca="false">AND(B9&lt;=MaxLaborCapacity,E9&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G9" s="31" t="n">
+      <c r="G9" s="35" t="n">
         <f aca="false">C9*FarmerRate</f>
-        <v>4865.1762796875</v>
-      </c>
-      <c r="H9" s="31" t="n">
+        <v>4865.48767089844</v>
+      </c>
+      <c r="H9" s="35" t="n">
         <f aca="false">D9*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I9" s="31" t="n">
+      <c r="I9" s="35" t="n">
         <f aca="false">$A9*Mes_Fert</f>
         <v>2640</v>
       </c>
-      <c r="J9" s="31" t="n">
+      <c r="J9" s="35" t="n">
         <f aca="false">G9+H9</f>
-        <v>4865.1762796875</v>
-      </c>
-      <c r="K9" s="31" t="n">
+        <v>4865.48767089844</v>
+      </c>
+      <c r="K9" s="35" t="n">
         <f aca="false">FixedCosts+I9+J9</f>
-        <v>27505.1762796875</v>
-      </c>
-      <c r="L9" s="31" t="n">
+        <v>27505.4876708984</v>
+      </c>
+      <c r="L9" s="35" t="n">
         <f aca="false">K9-K8</f>
-        <v>2541.7680296875</v>
-      </c>
-      <c r="M9" s="31" t="n">
+        <v>2541.87438964844</v>
+      </c>
+      <c r="M9" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N9" s="30" t="b">
+      <c r="N9" s="34" t="b">
         <f aca="false">L9&lt;=M9</f>
         <v>1</v>
       </c>
-      <c r="O9" s="31" t="n">
+      <c r="O9" s="35" t="n">
         <f aca="false">ABS(M9-L9)</f>
-        <v>158.231970312503</v>
+        <v>158.125610351563</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="29" t="n">
+      <c r="B10" s="33" t="n">
         <f aca="false">IF($A10=0,0,$A10*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A10)</f>
         <v>189.170160644531</v>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="33" t="n">
         <f aca="false">MIN(B10,FarmerHours)</f>
         <v>189.170160644531</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="33" t="n">
         <f aca="false">MAX(B10-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -5566,60 +5712,60 @@
         <f aca="false">IF(D10=0,0,ROUNDUP(D10/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F10" s="30" t="b">
+      <c r="F10" s="34" t="b">
         <f aca="false">AND(B10&lt;=MaxLaborCapacity,E10&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G10" s="31" t="n">
+      <c r="G10" s="35" t="n">
         <f aca="false">C10*FarmerRate</f>
-        <v>6567.98797757812</v>
-      </c>
-      <c r="H10" s="31" t="n">
+        <v>6568.40835571289</v>
+      </c>
+      <c r="H10" s="35" t="n">
         <f aca="false">D10*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I10" s="31" t="n">
+      <c r="I10" s="35" t="n">
         <f aca="false">$A10*Mes_Fert</f>
         <v>3520</v>
       </c>
-      <c r="J10" s="31" t="n">
+      <c r="J10" s="35" t="n">
         <f aca="false">G10+H10</f>
-        <v>6567.98797757812</v>
-      </c>
-      <c r="K10" s="31" t="n">
+        <v>6568.40835571289</v>
+      </c>
+      <c r="K10" s="35" t="n">
         <f aca="false">FixedCosts+I10+J10</f>
-        <v>30087.9879775781</v>
-      </c>
-      <c r="L10" s="31" t="n">
+        <v>30088.4083557129</v>
+      </c>
+      <c r="L10" s="35" t="n">
         <f aca="false">K10-K9</f>
-        <v>2582.81169789063</v>
-      </c>
-      <c r="M10" s="31" t="n">
+        <v>2582.92068481445</v>
+      </c>
+      <c r="M10" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N10" s="30" t="b">
+      <c r="N10" s="34" t="b">
         <f aca="false">L10&lt;=M10</f>
         <v>1</v>
       </c>
-      <c r="O10" s="31" t="n">
+      <c r="O10" s="35" t="n">
         <f aca="false">ABS(M10-L10)</f>
-        <v>117.188302109374</v>
+        <v>117.079315185547</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="29" t="n">
+      <c r="B11" s="33" t="n">
         <f aca="false">IF($A11=0,0,$A11*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A11)</f>
         <v>239.418484565735</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="33" t="n">
         <f aca="false">MIN(B11,FarmerHours)</f>
         <v>239.418484565735</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="33" t="n">
         <f aca="false">MAX(B11-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -5627,60 +5773,60 @@
         <f aca="false">IF(D11=0,0,ROUNDUP(D11/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F11" s="30" t="b">
+      <c r="F11" s="34" t="b">
         <f aca="false">AND(B11&lt;=MaxLaborCapacity,E11&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G11" s="31" t="n">
+      <c r="G11" s="35" t="n">
         <f aca="false">C11*FarmerRate</f>
-        <v>8312.60978412231</v>
-      </c>
-      <c r="H11" s="31" t="n">
+        <v>8313.14182519913</v>
+      </c>
+      <c r="H11" s="35" t="n">
         <f aca="false">D11*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I11" s="31" t="n">
+      <c r="I11" s="35" t="n">
         <f aca="false">$A11*Mes_Fert</f>
         <v>4400</v>
       </c>
-      <c r="J11" s="31" t="n">
+      <c r="J11" s="35" t="n">
         <f aca="false">G11+H11</f>
-        <v>8312.60978412231</v>
-      </c>
-      <c r="K11" s="31" t="n">
+        <v>8313.14182519913</v>
+      </c>
+      <c r="K11" s="35" t="n">
         <f aca="false">FixedCosts+I11+J11</f>
-        <v>32712.6097841223</v>
-      </c>
-      <c r="L11" s="31" t="n">
+        <v>32713.1418251991</v>
+      </c>
+      <c r="L11" s="35" t="n">
         <f aca="false">K11-K10</f>
-        <v>2624.62180654419</v>
-      </c>
-      <c r="M11" s="31" t="n">
+        <v>2624.73346948624</v>
+      </c>
+      <c r="M11" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N11" s="30" t="b">
+      <c r="N11" s="34" t="b">
         <f aca="false">L11&lt;=M11</f>
         <v>1</v>
       </c>
-      <c r="O11" s="31" t="n">
+      <c r="O11" s="35" t="n">
         <f aca="false">ABS(M11-L11)</f>
-        <v>75.3781934558101</v>
+        <v>75.2665305137634</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="29" t="n">
+      <c r="B12" s="33" t="n">
         <f aca="false">IF($A12=0,0,$A12*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A12)</f>
         <v>290.893458747368</v>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="33" t="n">
         <f aca="false">MIN(B12,FarmerHours)</f>
         <v>290.893458747368</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="33" t="n">
         <f aca="false">MAX(B12-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -5688,60 +5834,60 @@
         <f aca="false">IF(D12=0,0,ROUNDUP(D12/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F12" s="30" t="b">
+      <c r="F12" s="34" t="b">
         <f aca="false">AND(B12&lt;=MaxLaborCapacity,E12&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G12" s="31" t="n">
+      <c r="G12" s="35" t="n">
         <f aca="false">C12*FarmerRate</f>
-        <v>10099.8208877086</v>
-      </c>
-      <c r="H12" s="31" t="n">
+        <v>10100.4673176169</v>
+      </c>
+      <c r="H12" s="35" t="n">
         <f aca="false">D12*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I12" s="31" t="n">
+      <c r="I12" s="35" t="n">
         <f aca="false">$A12*Mes_Fert</f>
         <v>5280</v>
       </c>
-      <c r="J12" s="31" t="n">
+      <c r="J12" s="35" t="n">
         <f aca="false">G12+H12</f>
-        <v>10099.8208877086</v>
-      </c>
-      <c r="K12" s="31" t="n">
+        <v>10100.4673176169</v>
+      </c>
+      <c r="K12" s="35" t="n">
         <f aca="false">FixedCosts+I12+J12</f>
-        <v>35379.8208877086</v>
-      </c>
-      <c r="L12" s="31" t="n">
+        <v>35380.4673176169</v>
+      </c>
+      <c r="L12" s="35" t="n">
         <f aca="false">K12-K11</f>
-        <v>2667.21110358629</v>
-      </c>
-      <c r="M12" s="31" t="n">
+        <v>2667.3254924178</v>
+      </c>
+      <c r="M12" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N12" s="30" t="b">
+      <c r="N12" s="34" t="b">
         <f aca="false">L12&lt;=M12</f>
         <v>1</v>
       </c>
-      <c r="O12" s="31" t="n">
+      <c r="O12" s="35" t="n">
         <f aca="false">ABS(M12-L12)</f>
-        <v>32.7888964137055</v>
+        <v>32.6745075821964</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="33" t="n">
         <f aca="false">IF($A13=0,0,$A13*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A13)</f>
         <v>343.617898145328</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="33" t="n">
         <f aca="false">MIN(B13,FarmerHours)</f>
         <v>343.617898145328</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="33" t="n">
         <f aca="false">MAX(B13-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -5749,60 +5895,60 @@
         <f aca="false">IF(D13=0,0,ROUNDUP(D13/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F13" s="30" t="b">
+      <c r="F13" s="34" t="b">
         <f aca="false">AND(B13&lt;=MaxLaborCapacity,E13&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G13" s="31" t="n">
+      <c r="G13" s="35" t="n">
         <f aca="false">C13*FarmerRate</f>
-        <v>11930.4134236058</v>
-      </c>
-      <c r="H13" s="31" t="n">
+        <v>11931.177018935</v>
+      </c>
+      <c r="H13" s="35" t="n">
         <f aca="false">D13*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I13" s="31" t="n">
+      <c r="I13" s="35" t="n">
         <f aca="false">$A13*Mes_Fert</f>
         <v>6160</v>
       </c>
-      <c r="J13" s="31" t="n">
+      <c r="J13" s="35" t="n">
         <f aca="false">G13+H13</f>
-        <v>11930.4134236058</v>
-      </c>
-      <c r="K13" s="31" t="n">
+        <v>11931.177018935</v>
+      </c>
+      <c r="K13" s="35" t="n">
         <f aca="false">FixedCosts+I13+J13</f>
-        <v>38090.4134236058</v>
-      </c>
-      <c r="L13" s="31" t="n">
+        <v>38091.177018935</v>
+      </c>
+      <c r="L13" s="35" t="n">
         <f aca="false">K13-K12</f>
-        <v>2710.59253589719</v>
-      </c>
-      <c r="M13" s="31" t="n">
+        <v>2710.70970131808</v>
+      </c>
+      <c r="M13" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N13" s="30" t="b">
+      <c r="N13" s="34" t="b">
         <f aca="false">L13&lt;=M13</f>
         <v>0</v>
       </c>
-      <c r="O13" s="31" t="n">
+      <c r="O13" s="35" t="n">
         <f aca="false">ABS(M13-L13)</f>
-        <v>10.5925358971872</v>
+        <v>10.7097013180755</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="29" t="n">
+      <c r="B14" s="33" t="n">
         <f aca="false">IF($A14=0,0,$A14*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A14)</f>
         <v>397.614996425308</v>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="33" t="n">
         <f aca="false">MIN(B14,FarmerHours)</f>
         <v>397.614996425308</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="33" t="n">
         <f aca="false">MAX(B14-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -5810,60 +5956,60 @@
         <f aca="false">IF(D14=0,0,ROUNDUP(D14/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F14" s="30" t="b">
+      <c r="F14" s="34" t="b">
         <f aca="false">AND(B14&lt;=MaxLaborCapacity,E14&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G14" s="31" t="n">
+      <c r="G14" s="35" t="n">
         <f aca="false">C14*FarmerRate</f>
-        <v>13805.1926758867</v>
-      </c>
-      <c r="H14" s="31" t="n">
+        <v>13806.0762647677</v>
+      </c>
+      <c r="H14" s="35" t="n">
         <f aca="false">D14*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I14" s="31" t="n">
+      <c r="I14" s="35" t="n">
         <f aca="false">$A14*Mes_Fert</f>
         <v>7040</v>
       </c>
-      <c r="J14" s="31" t="n">
+      <c r="J14" s="35" t="n">
         <f aca="false">G14+H14</f>
-        <v>13805.1926758867</v>
-      </c>
-      <c r="K14" s="31" t="n">
+        <v>13806.0762647677</v>
+      </c>
+      <c r="K14" s="35" t="n">
         <f aca="false">FixedCosts+I14+J14</f>
-        <v>40845.1926758867</v>
-      </c>
-      <c r="L14" s="31" t="n">
+        <v>40846.0762647676</v>
+      </c>
+      <c r="L14" s="35" t="n">
         <f aca="false">K14-K13</f>
-        <v>2754.77925228091</v>
-      </c>
-      <c r="M14" s="31" t="n">
+        <v>2754.89924583264</v>
+      </c>
+      <c r="M14" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N14" s="30" t="b">
+      <c r="N14" s="34" t="b">
         <f aca="false">L14&lt;=M14</f>
         <v>0</v>
       </c>
-      <c r="O14" s="31" t="n">
+      <c r="O14" s="35" t="n">
         <f aca="false">ABS(M14-L14)</f>
-        <v>54.7792522809104</v>
+        <v>54.8992458326393</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="33" t="n">
         <f aca="false">IF($A15=0,0,$A15*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A15)</f>
         <v>452.908331865703</v>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="33" t="n">
         <f aca="false">MIN(B15,FarmerHours)</f>
         <v>452.908331865703</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="33" t="n">
         <f aca="false">MAX(B15-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -5871,60 +6017,60 @@
         <f aca="false">IF(D15=0,0,ROUNDUP(D15/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F15" s="30" t="b">
+      <c r="F15" s="34" t="b">
         <f aca="false">AND(B15&lt;=MaxLaborCapacity,E15&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G15" s="31" t="n">
+      <c r="G15" s="35" t="n">
         <f aca="false">C15*FarmerRate</f>
-        <v>15724.9772823772</v>
-      </c>
-      <c r="H15" s="31" t="n">
+        <v>15725.9837453369</v>
+      </c>
+      <c r="H15" s="35" t="n">
         <f aca="false">D15*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I15" s="31" t="n">
+      <c r="I15" s="35" t="n">
         <f aca="false">$A15*Mes_Fert</f>
         <v>7920</v>
       </c>
-      <c r="J15" s="31" t="n">
+      <c r="J15" s="35" t="n">
         <f aca="false">G15+H15</f>
-        <v>15724.9772823772</v>
-      </c>
-      <c r="K15" s="31" t="n">
+        <v>15725.9837453369</v>
+      </c>
+      <c r="K15" s="35" t="n">
         <f aca="false">FixedCosts+I15+J15</f>
-        <v>43644.9772823772</v>
-      </c>
-      <c r="L15" s="31" t="n">
+        <v>43645.9837453369</v>
+      </c>
+      <c r="L15" s="35" t="n">
         <f aca="false">K15-K14</f>
-        <v>2799.7846064905</v>
-      </c>
-      <c r="M15" s="31" t="n">
+        <v>2799.90748056925</v>
+      </c>
+      <c r="M15" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N15" s="30" t="b">
+      <c r="N15" s="34" t="b">
         <f aca="false">L15&lt;=M15</f>
         <v>0</v>
       </c>
-      <c r="O15" s="31" t="n">
+      <c r="O15" s="35" t="n">
         <f aca="false">ABS(M15-L15)</f>
-        <v>99.7846064904952</v>
+        <v>99.9074805692508</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="29" t="n">
+      <c r="B16" s="33" t="n">
         <f aca="false">IF($A16=0,0,$A16*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A16)</f>
         <v>509.521873348916</v>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="33" t="n">
         <f aca="false">MIN(B16,FarmerHours)</f>
         <v>509.521873348916</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="33" t="n">
         <f aca="false">MAX(B16-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -5932,60 +6078,60 @@
         <f aca="false">IF(D16=0,0,ROUNDUP(D16/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F16" s="30" t="b">
+      <c r="F16" s="34" t="b">
         <f aca="false">AND(B16&lt;=MaxLaborCapacity,E16&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G16" s="31" t="n">
+      <c r="G16" s="35" t="n">
         <f aca="false">C16*FarmerRate</f>
-        <v>17690.5994426743</v>
-      </c>
-      <c r="H16" s="31" t="n">
+        <v>17691.731713504</v>
+      </c>
+      <c r="H16" s="35" t="n">
         <f aca="false">D16*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I16" s="31" t="n">
+      <c r="I16" s="35" t="n">
         <f aca="false">$A16*Mes_Fert</f>
         <v>8800</v>
       </c>
-      <c r="J16" s="31" t="n">
+      <c r="J16" s="35" t="n">
         <f aca="false">G16+H16</f>
-        <v>17690.5994426743</v>
-      </c>
-      <c r="K16" s="31" t="n">
+        <v>17691.731713504</v>
+      </c>
+      <c r="K16" s="35" t="n">
         <f aca="false">FixedCosts+I16+J16</f>
-        <v>46490.5994426743</v>
-      </c>
-      <c r="L16" s="31" t="n">
+        <v>46491.731713504</v>
+      </c>
+      <c r="L16" s="35" t="n">
         <f aca="false">K16-K15</f>
-        <v>2845.62216029714</v>
-      </c>
-      <c r="M16" s="31" t="n">
+        <v>2845.74796816711</v>
+      </c>
+      <c r="M16" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N16" s="30" t="b">
+      <c r="N16" s="34" t="b">
         <f aca="false">L16&lt;=M16</f>
         <v>0</v>
       </c>
-      <c r="O16" s="31" t="n">
+      <c r="O16" s="35" t="n">
         <f aca="false">ABS(M16-L16)</f>
-        <v>145.622160297142</v>
+        <v>145.74796816711</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="33" t="n">
         <f aca="false">IF($A17=0,0,$A17*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A17)</f>
         <v>567.479986442355</v>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="33" t="n">
         <f aca="false">MIN(B17,FarmerHours)</f>
         <v>567.479986442355</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="33" t="n">
         <f aca="false">MAX(B17-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -5993,60 +6139,60 @@
         <f aca="false">IF(D17=0,0,ROUNDUP(D17/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F17" s="30" t="b">
+      <c r="F17" s="34" t="b">
         <f aca="false">AND(B17&lt;=MaxLaborCapacity,E17&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G17" s="31" t="n">
+      <c r="G17" s="35" t="n">
         <f aca="false">C17*FarmerRate</f>
-        <v>19702.9051292786</v>
-      </c>
-      <c r="H17" s="31" t="n">
+        <v>19704.1661959151</v>
+      </c>
+      <c r="H17" s="35" t="n">
         <f aca="false">D17*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I17" s="31" t="n">
+      <c r="I17" s="35" t="n">
         <f aca="false">$A17*Mes_Fert</f>
         <v>9680</v>
       </c>
-      <c r="J17" s="31" t="n">
+      <c r="J17" s="35" t="n">
         <f aca="false">G17+H17</f>
-        <v>19702.9051292786</v>
-      </c>
-      <c r="K17" s="31" t="n">
+        <v>19704.1661959151</v>
+      </c>
+      <c r="K17" s="35" t="n">
         <f aca="false">FixedCosts+I17+J17</f>
-        <v>49382.9051292786</v>
-      </c>
-      <c r="L17" s="31" t="n">
+        <v>49384.1661959151</v>
+      </c>
+      <c r="L17" s="35" t="n">
         <f aca="false">K17-K16</f>
-        <v>2892.30568660421</v>
-      </c>
-      <c r="M17" s="31" t="n">
+        <v>2892.43448241109</v>
+      </c>
+      <c r="M17" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N17" s="30" t="b">
+      <c r="N17" s="34" t="b">
         <f aca="false">L17&lt;=M17</f>
         <v>0</v>
       </c>
-      <c r="O17" s="31" t="n">
+      <c r="O17" s="35" t="n">
         <f aca="false">ABS(M17-L17)</f>
-        <v>192.30568660421</v>
+        <v>192.434482411089</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="29" t="n">
+      <c r="B18" s="33" t="n">
         <f aca="false">IF($A18=0,0,$A18*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A18)</f>
         <v>626.807439570419</v>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="33" t="n">
         <f aca="false">MIN(B18,FarmerHours)</f>
         <v>626.807439570419</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="33" t="n">
         <f aca="false">MAX(B18-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -6054,60 +6200,60 @@
         <f aca="false">IF(D18=0,0,ROUNDUP(D18/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F18" s="30" t="b">
+      <c r="F18" s="34" t="b">
         <f aca="false">AND(B18&lt;=MaxLaborCapacity,E18&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G18" s="31" t="n">
+      <c r="G18" s="35" t="n">
         <f aca="false">C18*FarmerRate</f>
-        <v>21762.7543018849</v>
-      </c>
-      <c r="H18" s="31" t="n">
+        <v>21764.1472073062</v>
+      </c>
+      <c r="H18" s="35" t="n">
         <f aca="false">D18*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I18" s="31" t="n">
+      <c r="I18" s="35" t="n">
         <f aca="false">$A18*Mes_Fert</f>
         <v>10560</v>
       </c>
-      <c r="J18" s="31" t="n">
+      <c r="J18" s="35" t="n">
         <f aca="false">G18+H18</f>
-        <v>21762.7543018849</v>
-      </c>
-      <c r="K18" s="31" t="n">
+        <v>21764.1472073062</v>
+      </c>
+      <c r="K18" s="35" t="n">
         <f aca="false">FixedCosts+I18+J18</f>
-        <v>52322.754301885</v>
-      </c>
-      <c r="L18" s="31" t="n">
+        <v>52324.1472073062</v>
+      </c>
+      <c r="L18" s="35" t="n">
         <f aca="false">K18-K17</f>
-        <v>2939.8491726064</v>
-      </c>
-      <c r="M18" s="31" t="n">
+        <v>2939.98101139112</v>
+      </c>
+      <c r="M18" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N18" s="30" t="b">
+      <c r="N18" s="34" t="b">
         <f aca="false">L18&lt;=M18</f>
         <v>0</v>
       </c>
-      <c r="O18" s="31" t="n">
+      <c r="O18" s="35" t="n">
         <f aca="false">ABS(M18-L18)</f>
-        <v>239.849172606395</v>
+        <v>239.981011391123</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="29" t="n">
+      <c r="B19" s="33" t="n">
         <f aca="false">IF($A19=0,0,$A19*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A19)</f>
         <v>687.529410278803</v>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="33" t="n">
         <f aca="false">MIN(B19,FarmerHours)</f>
         <v>687.529410278803</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="33" t="n">
         <f aca="false">MAX(B19-FarmerHours,0)</f>
         <v>0</v>
       </c>
@@ -6115,60 +6261,60 @@
         <f aca="false">IF(D19=0,0,ROUNDUP(D19/TempWorkerHours,0))</f>
         <v>0</v>
       </c>
-      <c r="F19" s="30" t="b">
+      <c r="F19" s="34" t="b">
         <f aca="false">AND(B19&lt;=MaxLaborCapacity,E19&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G19" s="31" t="n">
+      <c r="G19" s="35" t="n">
         <f aca="false">C19*FarmerRate</f>
-        <v>23871.0211248801</v>
-      </c>
-      <c r="H19" s="31" t="n">
+        <v>23872.548968014</v>
+      </c>
+      <c r="H19" s="35" t="n">
         <f aca="false">D19*TempRate</f>
         <v>0</v>
       </c>
-      <c r="I19" s="31" t="n">
+      <c r="I19" s="35" t="n">
         <f aca="false">$A19*Mes_Fert</f>
         <v>11440</v>
       </c>
-      <c r="J19" s="31" t="n">
+      <c r="J19" s="35" t="n">
         <f aca="false">G19+H19</f>
-        <v>23871.0211248801</v>
-      </c>
-      <c r="K19" s="31" t="n">
+        <v>23872.548968014</v>
+      </c>
+      <c r="K19" s="35" t="n">
         <f aca="false">FixedCosts+I19+J19</f>
-        <v>55311.0211248801</v>
-      </c>
-      <c r="L19" s="31" t="n">
+        <v>55312.548968014</v>
+      </c>
+      <c r="L19" s="35" t="n">
         <f aca="false">K19-K18</f>
-        <v>2988.2668229951</v>
-      </c>
-      <c r="M19" s="31" t="n">
+        <v>2988.40176070778</v>
+      </c>
+      <c r="M19" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N19" s="30" t="b">
+      <c r="N19" s="34" t="b">
         <f aca="false">L19&lt;=M19</f>
         <v>0</v>
       </c>
-      <c r="O19" s="31" t="n">
+      <c r="O19" s="35" t="n">
         <f aca="false">ABS(M19-L19)</f>
-        <v>288.266822995101</v>
+        <v>288.401760707784</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="29" t="n">
+      <c r="B20" s="33" t="n">
         <f aca="false">IF($A20=0,0,$A20*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A20)</f>
         <v>749.671491592464</v>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="33" t="n">
         <f aca="false">MIN(B20,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="33" t="n">
         <f aca="false">MAX(B20-FarmerHours,0)</f>
         <v>29.6714915924644</v>
       </c>
@@ -6176,60 +6322,60 @@
         <f aca="false">IF(D20=0,0,ROUNDUP(D20/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F20" s="30" t="b">
+      <c r="F20" s="34" t="b">
         <f aca="false">AND(B20&lt;=MaxLaborCapacity,E20&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G20" s="31" t="n">
+      <c r="G20" s="35" t="n">
         <f aca="false">C20*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H20" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H20" s="35" t="n">
         <f aca="false">D20*TempRate</f>
-        <v>515.097094045181</v>
-      </c>
-      <c r="I20" s="31" t="n">
+        <v>515.130062369173</v>
+      </c>
+      <c r="I20" s="35" t="n">
         <f aca="false">$A20*Mes_Fert</f>
         <v>12320</v>
       </c>
-      <c r="J20" s="31" t="n">
+      <c r="J20" s="35" t="n">
         <f aca="false">G20+H20</f>
-        <v>25513.4970940452</v>
-      </c>
-      <c r="K20" s="31" t="n">
+        <v>25515.1300623692</v>
+      </c>
+      <c r="K20" s="35" t="n">
         <f aca="false">FixedCosts+I20+J20</f>
-        <v>57833.4970940452</v>
-      </c>
-      <c r="L20" s="31" t="n">
+        <v>57835.1300623692</v>
+      </c>
+      <c r="L20" s="35" t="n">
         <f aca="false">K20-K19</f>
-        <v>2522.47596916513</v>
-      </c>
-      <c r="M20" s="31" t="n">
+        <v>2522.58109435517</v>
+      </c>
+      <c r="M20" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N20" s="30" t="b">
+      <c r="N20" s="34" t="b">
         <f aca="false">L20&lt;=M20</f>
         <v>1</v>
       </c>
-      <c r="O20" s="31" t="n">
+      <c r="O20" s="35" t="n">
         <f aca="false">ABS(M20-L20)</f>
-        <v>177.524030834873</v>
+        <v>177.41890564483</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="29" t="n">
+      <c r="B21" s="33" t="n">
         <f aca="false">IF($A21=0,0,$A21*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A21)</f>
         <v>813.259698468611</v>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="33" t="n">
         <f aca="false">MIN(B21,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="33" t="n">
         <f aca="false">MAX(B21-FarmerHours,0)</f>
         <v>93.2596984686107</v>
       </c>
@@ -6237,60 +6383,60 @@
         <f aca="false">IF(D21=0,0,ROUNDUP(D21/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F21" s="30" t="b">
+      <c r="F21" s="34" t="b">
         <f aca="false">AND(B21&lt;=MaxLaborCapacity,E21&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G21" s="31" t="n">
+      <c r="G21" s="35" t="n">
         <f aca="false">C21*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H21" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H21" s="35" t="n">
         <f aca="false">D21*TempRate</f>
-        <v>1618.98836541508</v>
-      </c>
-      <c r="I21" s="31" t="n">
+        <v>1619.09198730227</v>
+      </c>
+      <c r="I21" s="35" t="n">
         <f aca="false">$A21*Mes_Fert</f>
         <v>13200</v>
       </c>
-      <c r="J21" s="31" t="n">
+      <c r="J21" s="35" t="n">
         <f aca="false">G21+H21</f>
-        <v>26617.3883654151</v>
-      </c>
-      <c r="K21" s="31" t="n">
+        <v>26619.0919873023</v>
+      </c>
+      <c r="K21" s="35" t="n">
         <f aca="false">FixedCosts+I21+J21</f>
-        <v>59817.3883654151</v>
-      </c>
-      <c r="L21" s="31" t="n">
+        <v>59819.0919873023</v>
+      </c>
+      <c r="L21" s="35" t="n">
         <f aca="false">K21-K20</f>
-        <v>1983.89127136991</v>
-      </c>
-      <c r="M21" s="31" t="n">
+        <v>1983.96192493309</v>
+      </c>
+      <c r="M21" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N21" s="30" t="b">
+      <c r="N21" s="34" t="b">
         <f aca="false">L21&lt;=M21</f>
         <v>1</v>
       </c>
-      <c r="O21" s="31" t="n">
+      <c r="O21" s="35" t="n">
         <f aca="false">ABS(M21-L21)</f>
-        <v>716.10872863009</v>
+        <v>716.038075066907</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="29" t="n">
+      <c r="B22" s="33" t="n">
         <f aca="false">IF($A22=0,0,$A22*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A22)</f>
         <v>878.3204743461</v>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="33" t="n">
         <f aca="false">MIN(B22,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="33" t="n">
         <f aca="false">MAX(B22-FarmerHours,0)</f>
         <v>158.3204743461</v>
       </c>
@@ -6298,60 +6444,60 @@
         <f aca="false">IF(D22=0,0,ROUNDUP(D22/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F22" s="30" t="b">
+      <c r="F22" s="34" t="b">
         <f aca="false">AND(B22&lt;=MaxLaborCapacity,E22&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G22" s="31" t="n">
+      <c r="G22" s="35" t="n">
         <f aca="false">C22*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H22" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H22" s="35" t="n">
         <f aca="false">D22*TempRate</f>
-        <v>2748.44343464829</v>
-      </c>
-      <c r="I22" s="31" t="n">
+        <v>2748.61934628645</v>
+      </c>
+      <c r="I22" s="35" t="n">
         <f aca="false">$A22*Mes_Fert</f>
         <v>14080</v>
       </c>
-      <c r="J22" s="31" t="n">
+      <c r="J22" s="35" t="n">
         <f aca="false">G22+H22</f>
-        <v>27746.8434346483</v>
-      </c>
-      <c r="K22" s="31" t="n">
+        <v>27748.6193462865</v>
+      </c>
+      <c r="K22" s="35" t="n">
         <f aca="false">FixedCosts+I22+J22</f>
-        <v>61826.8434346483</v>
-      </c>
-      <c r="L22" s="31" t="n">
+        <v>61828.6193462865</v>
+      </c>
+      <c r="L22" s="35" t="n">
         <f aca="false">K22-K21</f>
-        <v>2009.45506923321</v>
-      </c>
-      <c r="M22" s="31" t="n">
+        <v>2009.52735898419</v>
+      </c>
+      <c r="M22" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N22" s="30" t="b">
+      <c r="N22" s="34" t="b">
         <f aca="false">L22&lt;=M22</f>
         <v>1</v>
       </c>
-      <c r="O22" s="31" t="n">
+      <c r="O22" s="35" t="n">
         <f aca="false">ABS(M22-L22)</f>
-        <v>690.544930766795</v>
+        <v>690.472641015811</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="29" t="n">
+      <c r="B23" s="33" t="n">
         <f aca="false">IF($A23=0,0,$A23*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A23)</f>
         <v>944.88069779264</v>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="33" t="n">
         <f aca="false">MIN(B23,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="33" t="n">
         <f aca="false">MAX(B23-FarmerHours,0)</f>
         <v>224.88069779264</v>
       </c>
@@ -6359,60 +6505,60 @@
         <f aca="false">IF(D23=0,0,ROUNDUP(D23/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F23" s="30" t="b">
+      <c r="F23" s="34" t="b">
         <f aca="false">AND(B23&lt;=MaxLaborCapacity,E23&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G23" s="31" t="n">
+      <c r="G23" s="35" t="n">
         <f aca="false">C23*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H23" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H23" s="35" t="n">
         <f aca="false">D23*TempRate</f>
-        <v>3903.92891368023</v>
-      </c>
-      <c r="I23" s="31" t="n">
+        <v>3904.17878112222</v>
+      </c>
+      <c r="I23" s="35" t="n">
         <f aca="false">$A23*Mes_Fert</f>
         <v>14960</v>
       </c>
-      <c r="J23" s="31" t="n">
+      <c r="J23" s="35" t="n">
         <f aca="false">G23+H23</f>
-        <v>28902.3289136802</v>
-      </c>
-      <c r="K23" s="31" t="n">
+        <v>28904.1787811222</v>
+      </c>
+      <c r="K23" s="35" t="n">
         <f aca="false">FixedCosts+I23+J23</f>
-        <v>63862.3289136802</v>
-      </c>
-      <c r="L23" s="31" t="n">
+        <v>63864.1787811222</v>
+      </c>
+      <c r="L23" s="35" t="n">
         <f aca="false">K23-K22</f>
-        <v>2035.48547903194</v>
-      </c>
-      <c r="M23" s="31" t="n">
+        <v>2035.55943483576</v>
+      </c>
+      <c r="M23" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N23" s="30" t="b">
+      <c r="N23" s="34" t="b">
         <f aca="false">L23&lt;=M23</f>
         <v>1</v>
       </c>
-      <c r="O23" s="31" t="n">
+      <c r="O23" s="35" t="n">
         <f aca="false">ABS(M23-L23)</f>
-        <v>664.514520968063</v>
+        <v>664.440565164237</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="29" t="n">
+      <c r="B24" s="33" t="n">
         <f aca="false">IF($A24=0,0,$A24*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A24)</f>
         <v>1012.96768925123</v>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="33" t="n">
         <f aca="false">MIN(B24,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="33" t="n">
         <f aca="false">MAX(B24-FarmerHours,0)</f>
         <v>292.967689251227</v>
       </c>
@@ -6420,60 +6566,60 @@
         <f aca="false">IF(D24=0,0,ROUNDUP(D24/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F24" s="30" t="b">
+      <c r="F24" s="34" t="b">
         <f aca="false">AND(B24&lt;=MaxLaborCapacity,E24&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G24" s="31" t="n">
+      <c r="G24" s="35" t="n">
         <f aca="false">C24*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H24" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H24" s="35" t="n">
         <f aca="false">D24*TempRate</f>
-        <v>5085.9190854013</v>
-      </c>
-      <c r="I24" s="31" t="n">
+        <v>5086.24460505603</v>
+      </c>
+      <c r="I24" s="35" t="n">
         <f aca="false">$A24*Mes_Fert</f>
         <v>15840</v>
       </c>
-      <c r="J24" s="31" t="n">
+      <c r="J24" s="35" t="n">
         <f aca="false">G24+H24</f>
-        <v>30084.3190854013</v>
-      </c>
-      <c r="K24" s="31" t="n">
+        <v>30086.244605056</v>
+      </c>
+      <c r="K24" s="35" t="n">
         <f aca="false">FixedCosts+I24+J24</f>
-        <v>65924.3190854013</v>
-      </c>
-      <c r="L24" s="31" t="n">
+        <v>65926.244605056</v>
+      </c>
+      <c r="L24" s="35" t="n">
         <f aca="false">K24-K23</f>
-        <v>2061.99017172108</v>
-      </c>
-      <c r="M24" s="31" t="n">
+        <v>2062.06582393381</v>
+      </c>
+      <c r="M24" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N24" s="30" t="b">
+      <c r="N24" s="34" t="b">
         <f aca="false">L24&lt;=M24</f>
         <v>1</v>
       </c>
-      <c r="O24" s="31" t="n">
+      <c r="O24" s="35" t="n">
         <f aca="false">ABS(M24-L24)</f>
-        <v>638.009828278919</v>
+        <v>637.934176066192</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="29" t="n">
+      <c r="B25" s="33" t="n">
         <f aca="false">IF($A25=0,0,$A25*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A25)</f>
         <v>1082.60921788725</v>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="33" t="n">
         <f aca="false">MIN(B25,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="33" t="n">
         <f aca="false">MAX(B25-FarmerHours,0)</f>
         <v>362.609217887249</v>
       </c>
@@ -6481,60 +6627,60 @@
         <f aca="false">IF(D25=0,0,ROUNDUP(D25/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F25" s="30" t="b">
+      <c r="F25" s="34" t="b">
         <f aca="false">AND(B25&lt;=MaxLaborCapacity,E25&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G25" s="31" t="n">
+      <c r="G25" s="35" t="n">
         <f aca="false">C25*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H25" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H25" s="35" t="n">
         <f aca="false">D25*TempRate</f>
-        <v>6294.89602252264</v>
-      </c>
-      <c r="I25" s="31" t="n">
+        <v>6295.29892165363</v>
+      </c>
+      <c r="I25" s="35" t="n">
         <f aca="false">$A25*Mes_Fert</f>
         <v>16720</v>
       </c>
-      <c r="J25" s="31" t="n">
+      <c r="J25" s="35" t="n">
         <f aca="false">G25+H25</f>
-        <v>31293.2960225226</v>
-      </c>
-      <c r="K25" s="31" t="n">
+        <v>31295.2989216536</v>
+      </c>
+      <c r="K25" s="35" t="n">
         <f aca="false">FixedCosts+I25+J25</f>
-        <v>68013.2960225226</v>
-      </c>
-      <c r="L25" s="31" t="n">
+        <v>68015.2989216536</v>
+      </c>
+      <c r="L25" s="35" t="n">
         <f aca="false">K25-K24</f>
-        <v>2088.97693712133</v>
-      </c>
-      <c r="M25" s="31" t="n">
+        <v>2089.0543165976</v>
+      </c>
+      <c r="M25" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N25" s="30" t="b">
+      <c r="N25" s="34" t="b">
         <f aca="false">L25&lt;=M25</f>
         <v>1</v>
       </c>
-      <c r="O25" s="31" t="n">
+      <c r="O25" s="35" t="n">
         <f aca="false">ABS(M25-L25)</f>
-        <v>611.023062878667</v>
+        <v>610.945683402402</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="29" t="n">
+      <c r="B26" s="33" t="n">
         <f aca="false">IF($A26=0,0,$A26*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A26)</f>
         <v>1153.83350853773</v>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="33" t="n">
         <f aca="false">MIN(B26,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="33" t="n">
         <f aca="false">MAX(B26-FarmerHours,0)</f>
         <v>433.833508537726</v>
       </c>
@@ -6542,60 +6688,60 @@
         <f aca="false">IF(D26=0,0,ROUNDUP(D26/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F26" s="30" t="b">
+      <c r="F26" s="34" t="b">
         <f aca="false">AND(B26&lt;=MaxLaborCapacity,E26&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G26" s="31" t="n">
+      <c r="G26" s="35" t="n">
         <f aca="false">C26*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H26" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H26" s="35" t="n">
         <f aca="false">D26*TempRate</f>
-        <v>7531.34970821492</v>
-      </c>
-      <c r="I26" s="31" t="n">
+        <v>7531.83174544663</v>
+      </c>
+      <c r="I26" s="35" t="n">
         <f aca="false">$A26*Mes_Fert</f>
         <v>17600</v>
       </c>
-      <c r="J26" s="31" t="n">
+      <c r="J26" s="35" t="n">
         <f aca="false">G26+H26</f>
-        <v>32529.7497082149</v>
-      </c>
-      <c r="K26" s="31" t="n">
+        <v>32531.8317454466</v>
+      </c>
+      <c r="K26" s="35" t="n">
         <f aca="false">FixedCosts+I26+J26</f>
-        <v>70129.7497082149</v>
-      </c>
-      <c r="L26" s="31" t="n">
+        <v>70131.8317454466</v>
+      </c>
+      <c r="L26" s="35" t="n">
         <f aca="false">K26-K25</f>
-        <v>2116.45368569228</v>
-      </c>
-      <c r="M26" s="31" t="n">
+        <v>2116.53282379301</v>
+      </c>
+      <c r="M26" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N26" s="30" t="b">
+      <c r="N26" s="34" t="b">
         <f aca="false">L26&lt;=M26</f>
         <v>1</v>
       </c>
-      <c r="O26" s="31" t="n">
+      <c r="O26" s="35" t="n">
         <f aca="false">ABS(M26-L26)</f>
-        <v>583.546314307721</v>
+        <v>583.467176206992</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="B27" s="29" t="n">
+      <c r="B27" s="33" t="n">
         <f aca="false">IF($A27=0,0,$A27*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A27)</f>
         <v>1226.66924876417</v>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="33" t="n">
         <f aca="false">MIN(B27,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="33" t="n">
         <f aca="false">MAX(B27-FarmerHours,0)</f>
         <v>506.66924876417</v>
       </c>
@@ -6603,60 +6749,60 @@
         <f aca="false">IF(D27=0,0,ROUNDUP(D27/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F27" s="30" t="b">
+      <c r="F27" s="34" t="b">
         <f aca="false">AND(B27&lt;=MaxLaborCapacity,E27&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G27" s="31" t="n">
+      <c r="G27" s="35" t="n">
         <f aca="false">C27*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H27" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H27" s="35" t="n">
         <f aca="false">D27*TempRate</f>
-        <v>8795.77815854599</v>
-      </c>
-      <c r="I27" s="31" t="n">
+        <v>8796.34112437795</v>
+      </c>
+      <c r="I27" s="35" t="n">
         <f aca="false">$A27*Mes_Fert</f>
         <v>18480</v>
       </c>
-      <c r="J27" s="31" t="n">
+      <c r="J27" s="35" t="n">
         <f aca="false">G27+H27</f>
-        <v>33794.178158546</v>
-      </c>
-      <c r="K27" s="31" t="n">
+        <v>33796.341124378</v>
+      </c>
+      <c r="K27" s="35" t="n">
         <f aca="false">FixedCosts+I27+J27</f>
-        <v>72274.178158546</v>
-      </c>
-      <c r="L27" s="31" t="n">
+        <v>72276.3411243779</v>
+      </c>
+      <c r="L27" s="35" t="n">
         <f aca="false">K27-K26</f>
-        <v>2144.42845033106</v>
-      </c>
-      <c r="M27" s="31" t="n">
+        <v>2144.50937893131</v>
+      </c>
+      <c r="M27" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N27" s="30" t="b">
+      <c r="N27" s="34" t="b">
         <f aca="false">L27&lt;=M27</f>
         <v>1</v>
       </c>
-      <c r="O27" s="31" t="n">
+      <c r="O27" s="35" t="n">
         <f aca="false">ABS(M27-L27)</f>
-        <v>555.571549668937</v>
+        <v>555.49062106869</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="B28" s="29" t="n">
+      <c r="B28" s="33" t="n">
         <f aca="false">IF($A28=0,0,$A28*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A28)</f>
         <v>1301.14559601057</v>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="33" t="n">
         <f aca="false">MIN(B28,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="33" t="n">
         <f aca="false">MAX(B28-FarmerHours,0)</f>
         <v>581.145596010566</v>
       </c>
@@ -6664,60 +6810,60 @@
         <f aca="false">IF(D28=0,0,ROUNDUP(D28/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F28" s="30" t="b">
+      <c r="F28" s="34" t="b">
         <f aca="false">AND(B28&lt;=MaxLaborCapacity,E28&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G28" s="31" t="n">
+      <c r="G28" s="35" t="n">
         <f aca="false">C28*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H28" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H28" s="35" t="n">
         <f aca="false">D28*TempRate</f>
-        <v>10088.6875467434</v>
-      </c>
-      <c r="I28" s="31" t="n">
+        <v>10089.3332640723</v>
+      </c>
+      <c r="I28" s="35" t="n">
         <f aca="false">$A28*Mes_Fert</f>
         <v>19360</v>
       </c>
-      <c r="J28" s="31" t="n">
+      <c r="J28" s="35" t="n">
         <f aca="false">G28+H28</f>
-        <v>35087.0875467434</v>
-      </c>
-      <c r="K28" s="31" t="n">
+        <v>35089.3332640723</v>
+      </c>
+      <c r="K28" s="35" t="n">
         <f aca="false">FixedCosts+I28+J28</f>
-        <v>74447.0875467434</v>
-      </c>
-      <c r="L28" s="31" t="n">
+        <v>74449.3332640723</v>
+      </c>
+      <c r="L28" s="35" t="n">
         <f aca="false">K28-K27</f>
-        <v>2172.90938819744</v>
-      </c>
-      <c r="M28" s="31" t="n">
+        <v>2172.99213969438</v>
+      </c>
+      <c r="M28" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N28" s="30" t="b">
+      <c r="N28" s="34" t="b">
         <f aca="false">L28&lt;=M28</f>
         <v>1</v>
       </c>
-      <c r="O28" s="31" t="n">
+      <c r="O28" s="35" t="n">
         <f aca="false">ABS(M28-L28)</f>
-        <v>527.09061180256</v>
+        <v>527.007860305617</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="B29" s="29" t="n">
+      <c r="B29" s="33" t="n">
         <f aca="false">IF($A29=0,0,$A29*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A29)</f>
         <v>1377.292184868</v>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="33" t="n">
         <f aca="false">MIN(B29,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="33" t="n">
         <f aca="false">MAX(B29-FarmerHours,0)</f>
         <v>657.292184868002</v>
       </c>
@@ -6725,60 +6871,60 @@
         <f aca="false">IF(D29=0,0,ROUNDUP(D29/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F29" s="30" t="b">
+      <c r="F29" s="34" t="b">
         <f aca="false">AND(B29&lt;=MaxLaborCapacity,E29&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G29" s="31" t="n">
+      <c r="G29" s="35" t="n">
         <f aca="false">C29*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H29" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H29" s="35" t="n">
         <f aca="false">D29*TempRate</f>
-        <v>11410.5923293085</v>
-      </c>
-      <c r="I29" s="31" t="n">
+        <v>11411.3226539584</v>
+      </c>
+      <c r="I29" s="35" t="n">
         <f aca="false">$A29*Mes_Fert</f>
         <v>20240</v>
       </c>
-      <c r="J29" s="31" t="n">
+      <c r="J29" s="35" t="n">
         <f aca="false">G29+H29</f>
-        <v>36408.9923293085</v>
-      </c>
-      <c r="K29" s="31" t="n">
+        <v>36411.3226539584</v>
+      </c>
+      <c r="K29" s="35" t="n">
         <f aca="false">FixedCosts+I29+J29</f>
-        <v>76648.9923293085</v>
-      </c>
-      <c r="L29" s="31" t="n">
+        <v>76651.3226539584</v>
+      </c>
+      <c r="L29" s="35" t="n">
         <f aca="false">K29-K28</f>
-        <v>2201.90478256509</v>
-      </c>
-      <c r="M29" s="31" t="n">
+        <v>2201.98938988605</v>
+      </c>
+      <c r="M29" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N29" s="30" t="b">
+      <c r="N29" s="34" t="b">
         <f aca="false">L29&lt;=M29</f>
         <v>1</v>
       </c>
-      <c r="O29" s="31" t="n">
+      <c r="O29" s="35" t="n">
         <f aca="false">ABS(M29-L29)</f>
-        <v>498.095217434908</v>
+        <v>498.010610113954</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="B30" s="29" t="n">
+      <c r="B30" s="33" t="n">
         <f aca="false">IF($A30=0,0,$A30*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A30)</f>
         <v>1455.1391344475</v>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="33" t="n">
         <f aca="false">MIN(B30,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="33" t="n">
         <f aca="false">MAX(B30-FarmerHours,0)</f>
         <v>735.139134447498</v>
       </c>
@@ -6786,60 +6932,60 @@
         <f aca="false">IF(D30=0,0,ROUNDUP(D30/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F30" s="30" t="b">
+      <c r="F30" s="34" t="b">
         <f aca="false">AND(B30&lt;=MaxLaborCapacity,E30&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G30" s="31" t="n">
+      <c r="G30" s="35" t="n">
         <f aca="false">C30*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H30" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H30" s="35" t="n">
         <f aca="false">D30*TempRate</f>
-        <v>12762.0153740086</v>
-      </c>
-      <c r="I30" s="31" t="n">
+        <v>12762.8321952691</v>
+      </c>
+      <c r="I30" s="35" t="n">
         <f aca="false">$A30*Mes_Fert</f>
         <v>21120</v>
       </c>
-      <c r="J30" s="31" t="n">
+      <c r="J30" s="35" t="n">
         <f aca="false">G30+H30</f>
-        <v>37760.4153740086</v>
-      </c>
-      <c r="K30" s="31" t="n">
+        <v>37762.8321952691</v>
+      </c>
+      <c r="K30" s="35" t="n">
         <f aca="false">FixedCosts+I30+J30</f>
-        <v>78880.4153740086</v>
-      </c>
-      <c r="L30" s="31" t="n">
+        <v>78882.8321952691</v>
+      </c>
+      <c r="L30" s="35" t="n">
         <f aca="false">K30-K29</f>
-        <v>2231.42304470004</v>
-      </c>
-      <c r="M30" s="31" t="n">
+        <v>2231.50954131069</v>
+      </c>
+      <c r="M30" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N30" s="30" t="b">
+      <c r="N30" s="34" t="b">
         <f aca="false">L30&lt;=M30</f>
         <v>1</v>
       </c>
-      <c r="O30" s="31" t="n">
+      <c r="O30" s="35" t="n">
         <f aca="false">ABS(M30-L30)</f>
-        <v>468.576955299955</v>
+        <v>468.49045868931</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="B31" s="29" t="n">
+      <c r="B31" s="33" t="n">
         <f aca="false">IF($A31=0,0,$A31*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A31)</f>
         <v>1534.7170558626</v>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="33" t="n">
         <f aca="false">MIN(B31,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="33" t="n">
         <f aca="false">MAX(B31-FarmerHours,0)</f>
         <v>814.717055862596</v>
       </c>
@@ -6847,60 +6993,60 @@
         <f aca="false">IF(D31=0,0,ROUNDUP(D31/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F31" s="30" t="b">
+      <c r="F31" s="34" t="b">
         <f aca="false">AND(B31&lt;=MaxLaborCapacity,E31&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G31" s="31" t="n">
+      <c r="G31" s="35" t="n">
         <f aca="false">C31*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H31" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H31" s="35" t="n">
         <f aca="false">D31*TempRate</f>
-        <v>14143.4880897747</v>
-      </c>
-      <c r="I31" s="31" t="n">
+        <v>14144.3933309478</v>
+      </c>
+      <c r="I31" s="35" t="n">
         <f aca="false">$A31*Mes_Fert</f>
         <v>22000</v>
       </c>
-      <c r="J31" s="31" t="n">
+      <c r="J31" s="35" t="n">
         <f aca="false">G31+H31</f>
-        <v>39141.8880897747</v>
-      </c>
-      <c r="K31" s="31" t="n">
+        <v>39144.3933309478</v>
+      </c>
+      <c r="K31" s="35" t="n">
         <f aca="false">FixedCosts+I31+J31</f>
-        <v>81141.8880897747</v>
-      </c>
-      <c r="L31" s="31" t="n">
+        <v>81144.3933309479</v>
+      </c>
+      <c r="L31" s="35" t="n">
         <f aca="false">K31-K30</f>
-        <v>2261.4727157661</v>
-      </c>
-      <c r="M31" s="31" t="n">
+        <v>2261.56113567879</v>
+      </c>
+      <c r="M31" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N31" s="30" t="b">
+      <c r="N31" s="34" t="b">
         <f aca="false">L31&lt;=M31</f>
         <v>1</v>
       </c>
-      <c r="O31" s="31" t="n">
+      <c r="O31" s="35" t="n">
         <f aca="false">ABS(M31-L31)</f>
-        <v>438.527284233904</v>
+        <v>438.438864321215</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="B32" s="29" t="n">
+      <c r="B32" s="33" t="n">
         <f aca="false">IF($A32=0,0,$A32*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A32)</f>
         <v>1616.05705982331</v>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="33" t="n">
         <f aca="false">MIN(B32,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="33" t="n">
         <f aca="false">MAX(B32-FarmerHours,0)</f>
         <v>896.057059823313</v>
       </c>
@@ -6908,60 +7054,60 @@
         <f aca="false">IF(D32=0,0,ROUNDUP(D32/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F32" s="30" t="b">
+      <c r="F32" s="34" t="b">
         <f aca="false">AND(B32&lt;=MaxLaborCapacity,E32&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G32" s="31" t="n">
+      <c r="G32" s="35" t="n">
         <f aca="false">C32*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H32" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H32" s="35" t="n">
         <f aca="false">D32*TempRate</f>
-        <v>15555.5505585327</v>
-      </c>
-      <c r="I32" s="31" t="n">
+        <v>15556.5461774881</v>
+      </c>
+      <c r="I32" s="35" t="n">
         <f aca="false">$A32*Mes_Fert</f>
         <v>22880</v>
       </c>
-      <c r="J32" s="31" t="n">
+      <c r="J32" s="35" t="n">
         <f aca="false">G32+H32</f>
-        <v>40553.9505585327</v>
-      </c>
-      <c r="K32" s="31" t="n">
+        <v>40556.5461774881</v>
+      </c>
+      <c r="K32" s="35" t="n">
         <f aca="false">FixedCosts+I32+J32</f>
-        <v>83433.9505585327</v>
-      </c>
-      <c r="L32" s="31" t="n">
+        <v>83436.5461774881</v>
+      </c>
+      <c r="L32" s="35" t="n">
         <f aca="false">K32-K31</f>
-        <v>2292.06246875804</v>
-      </c>
-      <c r="M32" s="31" t="n">
+        <v>2292.15284654022</v>
+      </c>
+      <c r="M32" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N32" s="30" t="b">
+      <c r="N32" s="34" t="b">
         <f aca="false">L32&lt;=M32</f>
         <v>1</v>
       </c>
-      <c r="O32" s="31" t="n">
+      <c r="O32" s="35" t="n">
         <f aca="false">ABS(M32-L32)</f>
-        <v>407.937531241958</v>
+        <v>407.847153459778</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="B33" s="29" t="n">
+      <c r="B33" s="33" t="n">
         <f aca="false">IF($A33=0,0,$A33*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A33)</f>
         <v>1699.19076434307</v>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="33" t="n">
         <f aca="false">MIN(B33,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="33" t="n">
         <f aca="false">MAX(B33-FarmerHours,0)</f>
         <v>979.19076434307</v>
       </c>
@@ -6969,60 +7115,60 @@
         <f aca="false">IF(D33=0,0,ROUNDUP(D33/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F33" s="30" t="b">
+      <c r="F33" s="34" t="b">
         <f aca="false">AND(B33&lt;=MaxLaborCapacity,E33&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G33" s="31" t="n">
+      <c r="G33" s="35" t="n">
         <f aca="false">C33*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H33" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H33" s="35" t="n">
         <f aca="false">D33*TempRate</f>
-        <v>16998.7516689957</v>
-      </c>
-      <c r="I33" s="31" t="n">
+        <v>16999.8396587339</v>
+      </c>
+      <c r="I33" s="35" t="n">
         <f aca="false">$A33*Mes_Fert</f>
         <v>23760</v>
       </c>
-      <c r="J33" s="31" t="n">
+      <c r="J33" s="35" t="n">
         <f aca="false">G33+H33</f>
-        <v>41997.1516689957</v>
-      </c>
-      <c r="K33" s="31" t="n">
+        <v>41999.8396587339</v>
+      </c>
+      <c r="K33" s="35" t="n">
         <f aca="false">FixedCosts+I33+J33</f>
-        <v>85757.1516689957</v>
-      </c>
-      <c r="L33" s="31" t="n">
+        <v>85759.8396587339</v>
+      </c>
+      <c r="L33" s="35" t="n">
         <f aca="false">K33-K32</f>
-        <v>2323.20111046299</v>
-      </c>
-      <c r="M33" s="31" t="n">
+        <v>2323.29348124578</v>
+      </c>
+      <c r="M33" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N33" s="30" t="b">
+      <c r="N33" s="34" t="b">
         <f aca="false">L33&lt;=M33</f>
         <v>1</v>
       </c>
-      <c r="O33" s="31" t="n">
+      <c r="O33" s="35" t="n">
         <f aca="false">ABS(M33-L33)</f>
-        <v>376.798889537007</v>
+        <v>376.706518754218</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="B34" s="29" t="n">
+      <c r="B34" s="33" t="n">
         <f aca="false">IF($A34=0,0,$A34*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A34)</f>
         <v>1784.15030256022</v>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="33" t="n">
         <f aca="false">MIN(B34,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="33" t="n">
         <f aca="false">MAX(B34-FarmerHours,0)</f>
         <v>1064.15030256022</v>
       </c>
@@ -7030,60 +7176,60 @@
         <f aca="false">IF(D34=0,0,ROUNDUP(D34/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F34" s="30" t="b">
+      <c r="F34" s="34" t="b">
         <f aca="false">AND(B34&lt;=MaxLaborCapacity,E34&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G34" s="31" t="n">
+      <c r="G34" s="35" t="n">
         <f aca="false">C34*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H34" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H34" s="35" t="n">
         <f aca="false">D34*TempRate</f>
-        <v>18473.6492524455</v>
-      </c>
-      <c r="I34" s="31" t="n">
+        <v>18474.8316416705</v>
+      </c>
+      <c r="I34" s="35" t="n">
         <f aca="false">$A34*Mes_Fert</f>
         <v>24640</v>
       </c>
-      <c r="J34" s="31" t="n">
+      <c r="J34" s="35" t="n">
         <f aca="false">G34+H34</f>
-        <v>43472.0492524455</v>
-      </c>
-      <c r="K34" s="31" t="n">
+        <v>43474.8316416705</v>
+      </c>
+      <c r="K34" s="35" t="n">
         <f aca="false">FixedCosts+I34+J34</f>
-        <v>88112.0492524455</v>
-      </c>
-      <c r="L34" s="31" t="n">
+        <v>88114.8316416706</v>
+      </c>
+      <c r="L34" s="35" t="n">
         <f aca="false">K34-K33</f>
-        <v>2354.89758344978</v>
-      </c>
-      <c r="M34" s="31" t="n">
+        <v>2354.9919829367</v>
+      </c>
+      <c r="M34" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N34" s="30" t="b">
+      <c r="N34" s="34" t="b">
         <f aca="false">L34&lt;=M34</f>
         <v>1</v>
       </c>
-      <c r="O34" s="31" t="n">
+      <c r="O34" s="35" t="n">
         <f aca="false">ABS(M34-L34)</f>
-        <v>345.102416550217</v>
+        <v>345.008017063301</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="B35" s="29" t="n">
+      <c r="B35" s="33" t="n">
         <f aca="false">IF($A35=0,0,$A35*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A35)</f>
         <v>1870.96833067588</v>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="33" t="n">
         <f aca="false">MIN(B35,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="33" t="n">
         <f aca="false">MAX(B35-FarmerHours,0)</f>
         <v>1150.96833067588</v>
       </c>
@@ -7091,60 +7237,60 @@
         <f aca="false">IF(D35=0,0,ROUNDUP(D35/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F35" s="30" t="b">
+      <c r="F35" s="34" t="b">
         <f aca="false">AND(B35&lt;=MaxLaborCapacity,E35&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G35" s="31" t="n">
+      <c r="G35" s="35" t="n">
         <f aca="false">C35*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H35" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H35" s="35" t="n">
         <f aca="false">D35*TempRate</f>
-        <v>19980.8102205332</v>
-      </c>
-      <c r="I35" s="31" t="n">
+        <v>19982.089074234</v>
+      </c>
+      <c r="I35" s="35" t="n">
         <f aca="false">$A35*Mes_Fert</f>
         <v>25520</v>
       </c>
-      <c r="J35" s="31" t="n">
+      <c r="J35" s="35" t="n">
         <f aca="false">G35+H35</f>
-        <v>44979.2102205332</v>
-      </c>
-      <c r="K35" s="31" t="n">
+        <v>44982.089074234</v>
+      </c>
+      <c r="K35" s="35" t="n">
         <f aca="false">FixedCosts+I35+J35</f>
-        <v>90499.2102205332</v>
-      </c>
-      <c r="L35" s="31" t="n">
+        <v>90502.089074234</v>
+      </c>
+      <c r="L35" s="35" t="n">
         <f aca="false">K35-K34</f>
-        <v>2387.16096808774</v>
-      </c>
-      <c r="M35" s="31" t="n">
+        <v>2387.25743256342</v>
+      </c>
+      <c r="M35" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N35" s="30" t="b">
+      <c r="N35" s="34" t="b">
         <f aca="false">L35&lt;=M35</f>
         <v>1</v>
       </c>
-      <c r="O35" s="31" t="n">
+      <c r="O35" s="35" t="n">
         <f aca="false">ABS(M35-L35)</f>
-        <v>312.839031912255</v>
+        <v>312.74256743658</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="B36" s="29" t="n">
+      <c r="B36" s="33" t="n">
         <f aca="false">IF($A36=0,0,$A36*Mes_BaseLabor*SeasonLength*(1+Mes_DR)^$A36)</f>
         <v>1959.67803600965</v>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="33" t="n">
         <f aca="false">MIN(B36,FarmerHours)</f>
         <v>720</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="33" t="n">
         <f aca="false">MAX(B36-FarmerHours,0)</f>
         <v>1239.67803600965</v>
       </c>
@@ -7152,45 +7298,45 @@
         <f aca="false">IF(D36=0,0,ROUNDUP(D36/TempWorkerHours,0))</f>
         <v>1</v>
       </c>
-      <c r="F36" s="30" t="b">
+      <c r="F36" s="34" t="b">
         <f aca="false">AND(B36&lt;=MaxLaborCapacity,E36&lt;=MaxTempWorkers)</f>
         <v>1</v>
       </c>
-      <c r="G36" s="31" t="n">
+      <c r="G36" s="35" t="n">
         <f aca="false">C36*FarmerRate</f>
-        <v>24998.4</v>
-      </c>
-      <c r="H36" s="31" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H36" s="35" t="n">
         <f aca="false">D36*TempRate</f>
-        <v>21520.8107051275</v>
-      </c>
-      <c r="I36" s="31" t="n">
+        <v>21522.1881251675</v>
+      </c>
+      <c r="I36" s="35" t="n">
         <f aca="false">$A36*Mes_Fert</f>
         <v>26400</v>
       </c>
-      <c r="J36" s="31" t="n">
+      <c r="J36" s="35" t="n">
         <f aca="false">G36+H36</f>
-        <v>46519.2107051275</v>
-      </c>
-      <c r="K36" s="31" t="n">
+        <v>46522.1881251675</v>
+      </c>
+      <c r="K36" s="35" t="n">
         <f aca="false">FixedCosts+I36+J36</f>
-        <v>92919.2107051275</v>
-      </c>
-      <c r="L36" s="31" t="n">
+        <v>92922.1881251675</v>
+      </c>
+      <c r="L36" s="35" t="n">
         <f aca="false">K36-K35</f>
-        <v>2420.00048459425</v>
-      </c>
-      <c r="M36" s="31" t="n">
+        <v>2420.09905093351</v>
+      </c>
+      <c r="M36" s="35" t="n">
         <f aca="false">Mes_Rev</f>
         <v>2700</v>
       </c>
-      <c r="N36" s="30" t="b">
+      <c r="N36" s="34" t="b">
         <f aca="false">L36&lt;=M36</f>
         <v>1</v>
       </c>
-      <c r="O36" s="31" t="n">
+      <c r="O36" s="35" t="n">
         <f aca="false">ABS(M36-L36)</f>
-        <v>279.999515405754</v>
+        <v>279.90094906649</v>
       </c>
     </row>
   </sheetData>
@@ -7241,7 +7387,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
@@ -7251,119 +7397,228 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B5" s="30" t="b">
+        <v>116</v>
+      </c>
+      <c r="B5" s="34" t="b">
         <f aca="false">AND(TomatoBeds=INT(TomatoBeds),TomatoBeds&gt;=0,TomatoBeds&lt;=Tom_Limit)</f>
         <v>1</v>
       </c>
-      <c r="C5" s="33" t="s">
-        <v>114</v>
+      <c r="C5" s="37" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" s="30" t="b">
+        <v>118</v>
+      </c>
+      <c r="B6" s="34" t="b">
         <f aca="false">AND(CarrotBeds=INT(CarrotBeds),CarrotBeds&gt;=0,CarrotBeds&lt;=Car_Limit)</f>
         <v>1</v>
       </c>
-      <c r="C6" s="33" t="s">
-        <v>116</v>
+      <c r="C6" s="37" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="30" t="b">
+        <v>120</v>
+      </c>
+      <c r="B7" s="34" t="b">
         <f aca="false">AND(MesclunBeds=INT(MesclunBeds),MesclunBeds&gt;=0,MesclunBeds&lt;=Mes_Limit)</f>
         <v>1</v>
       </c>
-      <c r="C7" s="33" t="s">
-        <v>118</v>
+      <c r="C7" s="37" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8" s="30" t="b">
+        <v>122</v>
+      </c>
+      <c r="B8" s="34" t="b">
         <f aca="false">TotalBedsUsed&lt;=TotalBeds</f>
         <v>1</v>
       </c>
-      <c r="C8" s="33" t="s">
-        <v>120</v>
+      <c r="C8" s="37" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B9" s="30" t="b">
+        <v>124</v>
+      </c>
+      <c r="B9" s="34" t="b">
         <f aca="false">TotalLaborRequired&lt;=TotalLaborCapacity</f>
         <v>1</v>
       </c>
-      <c r="C9" s="33" t="s">
-        <v>122</v>
+      <c r="C9" s="37" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B10" s="30" t="b">
+        <v>126</v>
+      </c>
+      <c r="B10" s="34" t="b">
         <f aca="false">TotalLaborRequired&lt;=MaxLaborCapacity</f>
         <v>1</v>
       </c>
-      <c r="C10" s="33" t="s">
-        <v>124</v>
+      <c r="C10" s="37" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B11" s="30" t="b">
+        <v>128</v>
+      </c>
+      <c r="B11" s="34" t="b">
         <f aca="false">TempWorkersNeeded&lt;=MaxTempWorkers</f>
         <v>1</v>
       </c>
-      <c r="C11" s="33" t="s">
-        <v>126</v>
+      <c r="C11" s="37" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="B13" s="30" t="b">
+        <v>130</v>
+      </c>
+      <c r="B13" s="34" t="b">
         <f aca="false">AND(B5,B6,B7,B8,B9,B10,B11)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="28" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="B17" s="38" t="b">
+        <f aca="false">'MC - Tomato'!B7=99</f>
+        <v>1</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="B18" s="38" t="b">
+        <f aca="false">ABS('MC - Tomato'!B16-2334.37)&lt;0.01</f>
+        <v>1</v>
+      </c>
+      <c r="C18" s="39" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="B19" s="38" t="b">
+        <f aca="false">AND(TomatoBeds=10,CarrotBeds=20,MesclunBeds=30)</f>
+        <v>1</v>
+      </c>
+      <c r="C19" s="39" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="38" t="b">
+        <f aca="false">ABS(SeasonProfit-42762)&lt;5</f>
+        <v>1</v>
+      </c>
+      <c r="C20" s="39" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" s="38" t="b">
+        <f aca="false">AND('MC - Tomato'!L16&lt;='MC - Tomato'!M16,'MC - Tomato'!L17&gt;'MC - Tomato'!M17)</f>
+        <v>1</v>
+      </c>
+      <c r="C21" s="39" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="B22" s="38" t="b">
+        <f aca="false">AND('MC - Carrot'!L16&lt;='MC - Carrot'!M16,'MC - Carrot'!L17&gt;'MC - Carrot'!M17)</f>
+        <v>1</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" s="38" t="b">
+        <f aca="false">AND('MC - Mesclun'!L12&lt;='MC - Mesclun'!M12,'MC - Mesclun'!L13&gt;'MC - Mesclun'!M13)</f>
+        <v>1</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="B25" s="38" t="b">
+        <f aca="false">AND(B17,B18,B19,B20,B21,B22,B23)</f>
         <v>1</v>
       </c>
     </row>
@@ -7436,6 +7691,70 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="cellIs" priority="18" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="19" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18">
+    <cfRule type="cellIs" priority="20" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="21" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19">
+    <cfRule type="cellIs" priority="22" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="23" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20">
+    <cfRule type="cellIs" priority="24" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="25" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21">
+    <cfRule type="cellIs" priority="26" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="27" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="cellIs" priority="28" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="29" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B23">
+    <cfRule type="cellIs" priority="30" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="31" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25">
+    <cfRule type="cellIs" priority="32" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="33" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -7458,68 +7777,68 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="34" t="s">
-        <v>128</v>
+      <c r="A1" s="41" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="35" t="s">
-        <v>130</v>
+      <c r="A4" s="42" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="35" t="s">
-        <v>132</v>
+      <c r="A7" s="42" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="35" t="s">
-        <v>134</v>
+      <c r="A10" s="42" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="35" t="s">
-        <v>136</v>
+      <c r="A13" s="42" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="35" t="s">
-        <v>138</v>
+      <c r="A16" s="42" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="35" t="s">
-        <v>140</v>
+      <c r="A19" s="42" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
